--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175111</v>
+        <v>124175534</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461897</v>
+        <v>461735</v>
       </c>
       <c r="R2" t="n">
-        <v>6700803</v>
+        <v>6701055</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124175498</v>
+        <v>124174911</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461876</v>
+        <v>461858</v>
       </c>
       <c r="R3" t="n">
-        <v>6700933</v>
+        <v>6700851</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -876,17 +871,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175739</v>
+        <v>124175381</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461713</v>
+        <v>461839</v>
       </c>
       <c r="R4" t="n">
-        <v>6701035</v>
+        <v>6700986</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124176170</v>
+        <v>124174681</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,30 +1018,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461712</v>
+        <v>461777</v>
       </c>
       <c r="R5" t="n">
-        <v>6700887</v>
+        <v>6700942</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1102,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124174932</v>
+        <v>124174707</v>
       </c>
       <c r="B6" t="n">
-        <v>91435</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,30 +1132,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461851</v>
+        <v>461884</v>
       </c>
       <c r="R6" t="n">
-        <v>6700848</v>
+        <v>6700921</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1208,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1227,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175266</v>
+        <v>124176170</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,24 +1254,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1270,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461917</v>
+        <v>461712</v>
       </c>
       <c r="R7" t="n">
-        <v>6700885</v>
+        <v>6700887</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124176373</v>
+        <v>124175050</v>
       </c>
       <c r="B8" t="n">
-        <v>92304</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,34 +1360,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461655</v>
+        <v>461862</v>
       </c>
       <c r="R8" t="n">
-        <v>6700853</v>
+        <v>6700845</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1443,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174911</v>
+        <v>124175959</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,26 +1479,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461858</v>
+        <v>461702</v>
       </c>
       <c r="R9" t="n">
-        <v>6700851</v>
+        <v>6701001</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1530,7 +1563,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1549,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124176290</v>
+        <v>124174869</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,39 +1593,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1601,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461688</v>
+        <v>461848</v>
       </c>
       <c r="R10" t="n">
-        <v>6700877</v>
+        <v>6700855</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1664,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175718</v>
+        <v>124176306</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,34 +1699,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461713</v>
+        <v>461677</v>
       </c>
       <c r="R11" t="n">
-        <v>6701043</v>
+        <v>6700883</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1774,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175959</v>
+        <v>124175075</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,43 +1814,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1830,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461702</v>
+        <v>461846</v>
       </c>
       <c r="R12" t="n">
-        <v>6701001</v>
+        <v>6700848</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1874,6 +1898,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1892,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124175050</v>
+        <v>124176021</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,39 +1929,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1944,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461862</v>
+        <v>461747</v>
       </c>
       <c r="R13" t="n">
-        <v>6700845</v>
+        <v>6700906</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2007,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175156</v>
+        <v>124175319</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2042,7 +2058,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2059,10 +2075,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461943</v>
+        <v>461910</v>
       </c>
       <c r="R14" t="n">
-        <v>6700846</v>
+        <v>6700899</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2122,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175381</v>
+        <v>124174890</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461839</v>
+        <v>461855</v>
       </c>
       <c r="R15" t="n">
-        <v>6700986</v>
+        <v>6700846</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2228,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124174707</v>
+        <v>124175718</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2266,17 +2282,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2284,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461884</v>
+        <v>461713</v>
       </c>
       <c r="R16" t="n">
-        <v>6700921</v>
+        <v>6701043</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2328,6 +2335,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175914</v>
+        <v>124175498</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,16 +2370,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2379,20 +2387,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461694</v>
+        <v>461876</v>
       </c>
       <c r="R17" t="n">
-        <v>6700999</v>
+        <v>6700933</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2438,6 +2438,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175776</v>
+        <v>124175453</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,34 +2481,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2511,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461720</v>
+        <v>461792</v>
       </c>
       <c r="R18" t="n">
-        <v>6701011</v>
+        <v>6700952</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2574,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175319</v>
+        <v>124175266</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,39 +2596,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2626,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461910</v>
+        <v>461917</v>
       </c>
       <c r="R19" t="n">
-        <v>6700899</v>
+        <v>6700885</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2689,7 +2690,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175587</v>
+        <v>124174819</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -2722,12 +2723,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2737,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461706</v>
+        <v>461833</v>
       </c>
       <c r="R20" t="n">
-        <v>6701095</v>
+        <v>6700849</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2767,17 +2776,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,7 +2808,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124175534</v>
+        <v>124176290</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2839,7 +2843,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2856,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461735</v>
+        <v>461688</v>
       </c>
       <c r="R21" t="n">
-        <v>6701055</v>
+        <v>6700877</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2919,10 +2923,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124174869</v>
+        <v>124175739</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,21 +2939,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2962,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461848</v>
+        <v>461713</v>
       </c>
       <c r="R22" t="n">
-        <v>6700855</v>
+        <v>6701035</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3025,10 +3029,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124174681</v>
+        <v>124176373</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>92304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,43 +3041,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461777</v>
+        <v>461655</v>
       </c>
       <c r="R23" t="n">
-        <v>6700942</v>
+        <v>6700853</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3125,6 +3120,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3143,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124175346</v>
+        <v>124175647</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,30 +3151,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461868</v>
+        <v>461689</v>
       </c>
       <c r="R24" t="n">
-        <v>6700927</v>
+        <v>6701105</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3230,7 +3235,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3249,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124176071</v>
+        <v>124175346</v>
       </c>
       <c r="B25" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,21 +3269,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3292,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461708</v>
+        <v>461868</v>
       </c>
       <c r="R25" t="n">
-        <v>6700899</v>
+        <v>6700927</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3355,10 +3359,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124174819</v>
+        <v>124175914</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3371,16 +3375,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3411,10 +3415,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461833</v>
+        <v>461694</v>
       </c>
       <c r="R26" t="n">
-        <v>6700849</v>
+        <v>6700999</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3473,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175647</v>
+        <v>124176275</v>
       </c>
       <c r="B27" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,39 +3489,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3525,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461689</v>
+        <v>461688</v>
       </c>
       <c r="R27" t="n">
-        <v>6701105</v>
+        <v>6700885</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3569,6 +3573,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3587,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124174890</v>
+        <v>124175111</v>
       </c>
       <c r="B28" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,30 +3604,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3630,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461855</v>
+        <v>461897</v>
       </c>
       <c r="R28" t="n">
-        <v>6700846</v>
+        <v>6700803</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3693,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124176306</v>
+        <v>124175587</v>
       </c>
       <c r="B29" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3705,39 +3719,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3745,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461677</v>
+        <v>461706</v>
       </c>
       <c r="R29" t="n">
-        <v>6700883</v>
+        <v>6701095</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3775,12 +3785,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,7 +3804,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3808,10 +3822,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124176275</v>
+        <v>124175215</v>
       </c>
       <c r="B30" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3820,39 +3834,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3860,10 +3865,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461688</v>
+        <v>461931</v>
       </c>
       <c r="R30" t="n">
-        <v>6700885</v>
+        <v>6700883</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3923,10 +3928,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175453</v>
+        <v>124175776</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,39 +3940,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461792</v>
+        <v>461720</v>
       </c>
       <c r="R31" t="n">
-        <v>6700952</v>
+        <v>6701011</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175215</v>
+        <v>124175156</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,30 +4050,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4081,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461931</v>
+        <v>461943</v>
       </c>
       <c r="R32" t="n">
-        <v>6700883</v>
+        <v>6700846</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4144,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124176021</v>
+        <v>124176071</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,21 +4169,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461747</v>
+        <v>461708</v>
       </c>
       <c r="R33" t="n">
-        <v>6700906</v>
+        <v>6700899</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4250,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175075</v>
+        <v>124174932</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
+        <v>91435</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4266,35 +4275,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461846</v>
+        <v>461851</v>
       </c>
       <c r="R34" t="n">
         <v>6700848</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175959</v>
+        <v>124174869</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461702</v>
+        <v>461848</v>
       </c>
       <c r="R2" t="n">
-        <v>6701001</v>
+        <v>6700855</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -775,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124174681</v>
+        <v>124175453</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,43 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461777</v>
+        <v>461792</v>
       </c>
       <c r="R3" t="n">
-        <v>6700942</v>
+        <v>6700952</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -893,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124176275</v>
+        <v>124175914</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,39 +908,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461688</v>
+        <v>461694</v>
       </c>
       <c r="R4" t="n">
-        <v>6700885</v>
+        <v>6700999</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1007,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175534</v>
+        <v>124176170</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,39 +1026,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461735</v>
+        <v>461712</v>
       </c>
       <c r="R5" t="n">
-        <v>6701055</v>
+        <v>6700887</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1141,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124176170</v>
+        <v>124175718</v>
       </c>
       <c r="B6" t="n">
         <v>91030</v>
@@ -1176,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1188,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461712</v>
+        <v>461713</v>
       </c>
       <c r="R6" t="n">
-        <v>6700887</v>
+        <v>6701043</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1251,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175914</v>
+        <v>124175111</v>
       </c>
       <c r="B7" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,43 +1246,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461694</v>
+        <v>461897</v>
       </c>
       <c r="R7" t="n">
-        <v>6700999</v>
+        <v>6700803</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1351,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124176290</v>
+        <v>124176306</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1404,7 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1421,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461688</v>
+        <v>461677</v>
       </c>
       <c r="R8" t="n">
-        <v>6700877</v>
+        <v>6700883</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1484,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174869</v>
+        <v>124174932</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461848</v>
+        <v>461851</v>
       </c>
       <c r="R9" t="n">
-        <v>6700855</v>
+        <v>6700848</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1590,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124175776</v>
+        <v>124174707</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1586,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1628,8 +1608,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461720</v>
+        <v>461884</v>
       </c>
       <c r="R10" t="n">
-        <v>6701011</v>
+        <v>6700921</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1681,7 +1670,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124174890</v>
+        <v>124175266</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461855</v>
+        <v>461917</v>
       </c>
       <c r="R11" t="n">
-        <v>6700846</v>
+        <v>6700885</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1806,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175050</v>
+        <v>124175647</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,39 +1806,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1858,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461862</v>
+        <v>461689</v>
       </c>
       <c r="R12" t="n">
-        <v>6700845</v>
+        <v>6701105</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1902,7 +1890,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1921,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124176306</v>
+        <v>124175959</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,39 +1920,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1973,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461677</v>
+        <v>461702</v>
       </c>
       <c r="R13" t="n">
-        <v>6700883</v>
+        <v>6701001</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2017,7 +2008,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2036,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175381</v>
+        <v>124175587</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,26 +2042,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2079,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461839</v>
+        <v>461706</v>
       </c>
       <c r="R14" t="n">
-        <v>6700986</v>
+        <v>6701095</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2109,12 +2104,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,7 +2123,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2142,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175075</v>
+        <v>124176071</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,39 +2153,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461846</v>
+        <v>461708</v>
       </c>
       <c r="R15" t="n">
-        <v>6700848</v>
+        <v>6700899</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2257,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175111</v>
+        <v>124175776</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,39 +2259,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2309,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461897</v>
+        <v>461720</v>
       </c>
       <c r="R16" t="n">
-        <v>6700803</v>
+        <v>6701011</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2372,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175156</v>
+        <v>124175346</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,39 +2369,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2424,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461943</v>
+        <v>461868</v>
       </c>
       <c r="R17" t="n">
-        <v>6700846</v>
+        <v>6700927</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2487,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124174819</v>
+        <v>124174911</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,39 +2479,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2543,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461833</v>
+        <v>461858</v>
       </c>
       <c r="R18" t="n">
-        <v>6700849</v>
+        <v>6700851</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2587,6 +2550,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2605,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124176021</v>
+        <v>124174681</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,26 +2585,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461747</v>
+        <v>461777</v>
       </c>
       <c r="R19" t="n">
-        <v>6700906</v>
+        <v>6700942</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2692,7 +2669,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2711,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175266</v>
+        <v>124174819</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,26 +2703,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2754,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461917</v>
+        <v>461833</v>
       </c>
       <c r="R20" t="n">
-        <v>6700885</v>
+        <v>6700849</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2798,7 +2787,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2817,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124176373</v>
+        <v>124175498</v>
       </c>
       <c r="B21" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,34 +2817,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2864,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461655</v>
+        <v>461876</v>
       </c>
       <c r="R21" t="n">
-        <v>6700853</v>
+        <v>6700933</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2902,13 +2891,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2927,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124175498</v>
+        <v>124175319</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2939,35 +2932,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2975,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461876</v>
+        <v>461910</v>
       </c>
       <c r="R22" t="n">
-        <v>6700933</v>
+        <v>6700899</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3013,17 +3010,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3042,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175739</v>
+        <v>124175075</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,30 +3047,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3085,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461713</v>
+        <v>461846</v>
       </c>
       <c r="R23" t="n">
-        <v>6701035</v>
+        <v>6700848</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3148,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124176071</v>
+        <v>124176373</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>92326</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,28 +3162,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3191,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461708</v>
+        <v>461655</v>
       </c>
       <c r="R24" t="n">
-        <v>6700899</v>
+        <v>6700853</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3254,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124174911</v>
+        <v>124175215</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3297,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461858</v>
+        <v>461931</v>
       </c>
       <c r="R25" t="n">
-        <v>6700851</v>
+        <v>6700883</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3360,7 +3366,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124175346</v>
+        <v>124176021</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3403,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461868</v>
+        <v>461747</v>
       </c>
       <c r="R26" t="n">
-        <v>6700927</v>
+        <v>6700906</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3466,10 +3472,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124174932</v>
+        <v>124175381</v>
       </c>
       <c r="B27" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3478,25 +3484,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461851</v>
+        <v>461839</v>
       </c>
       <c r="R27" t="n">
-        <v>6700848</v>
+        <v>6700986</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3572,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124174707</v>
+        <v>124175050</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3584,43 +3590,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3628,10 +3630,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461884</v>
+        <v>461862</v>
       </c>
       <c r="R28" t="n">
-        <v>6700921</v>
+        <v>6700845</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3672,6 +3674,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3690,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124175647</v>
+        <v>124176290</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,39 +3705,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3742,10 +3745,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461689</v>
+        <v>461688</v>
       </c>
       <c r="R29" t="n">
-        <v>6701105</v>
+        <v>6700877</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3786,6 +3789,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3804,10 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175587</v>
+        <v>124175156</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,35 +3820,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3852,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461706</v>
+        <v>461943</v>
       </c>
       <c r="R30" t="n">
-        <v>6701095</v>
+        <v>6700846</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3882,17 +3890,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,6 +3904,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3919,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175718</v>
+        <v>124176275</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3931,34 +3935,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3966,10 +3975,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461713</v>
+        <v>461688</v>
       </c>
       <c r="R31" t="n">
-        <v>6701043</v>
+        <v>6700885</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4029,7 +4038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175319</v>
+        <v>124175534</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4064,7 +4073,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4081,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461910</v>
+        <v>461735</v>
       </c>
       <c r="R32" t="n">
-        <v>6700899</v>
+        <v>6701055</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4144,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175215</v>
+        <v>124174890</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,21 +4169,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461931</v>
+        <v>461855</v>
       </c>
       <c r="R33" t="n">
-        <v>6700883</v>
+        <v>6700846</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4250,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175453</v>
+        <v>124175739</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4262,39 +4271,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461792</v>
+        <v>461713</v>
       </c>
       <c r="R34" t="n">
-        <v>6700952</v>
+        <v>6701035</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124174869</v>
+        <v>124176306</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461848</v>
+        <v>461677</v>
       </c>
       <c r="R2" t="n">
-        <v>6700855</v>
+        <v>6700883</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124175453</v>
+        <v>124175776</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +802,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461792</v>
+        <v>461720</v>
       </c>
       <c r="R3" t="n">
-        <v>6700952</v>
+        <v>6701011</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175914</v>
+        <v>124175959</v>
       </c>
       <c r="B4" t="n">
         <v>57519</v>
@@ -937,7 +941,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -952,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461694</v>
+        <v>461702</v>
       </c>
       <c r="R4" t="n">
-        <v>6700999</v>
+        <v>6701001</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175718</v>
+        <v>124175453</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,34 +1140,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461713</v>
+        <v>461792</v>
       </c>
       <c r="R6" t="n">
-        <v>6701043</v>
+        <v>6700952</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1234,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175111</v>
+        <v>124175156</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1286,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461897</v>
+        <v>461943</v>
       </c>
       <c r="R7" t="n">
-        <v>6700803</v>
+        <v>6700846</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1349,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124176306</v>
+        <v>124175075</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1401,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461677</v>
+        <v>461846</v>
       </c>
       <c r="R8" t="n">
-        <v>6700883</v>
+        <v>6700848</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1464,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174932</v>
+        <v>124176290</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,26 +1489,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461851</v>
+        <v>461688</v>
       </c>
       <c r="R9" t="n">
-        <v>6700848</v>
+        <v>6700877</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1570,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124174707</v>
+        <v>124174869</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,39 +1604,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461884</v>
+        <v>461848</v>
       </c>
       <c r="R10" t="n">
-        <v>6700921</v>
+        <v>6700855</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1670,6 +1675,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1688,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175266</v>
+        <v>124176071</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1710,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461917</v>
+        <v>461708</v>
       </c>
       <c r="R11" t="n">
-        <v>6700885</v>
+        <v>6700899</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1794,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175647</v>
+        <v>124175346</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,39 +1812,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461689</v>
+        <v>461868</v>
       </c>
       <c r="R12" t="n">
-        <v>6701105</v>
+        <v>6700927</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1890,6 +1887,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124175959</v>
+        <v>124175050</v>
       </c>
       <c r="B13" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,43 +1918,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1964,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461702</v>
+        <v>461862</v>
       </c>
       <c r="R13" t="n">
-        <v>6701001</v>
+        <v>6700845</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2008,6 +2002,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175587</v>
+        <v>124175111</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,35 +2033,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461706</v>
+        <v>461897</v>
       </c>
       <c r="R14" t="n">
-        <v>6701095</v>
+        <v>6700803</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2104,17 +2103,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,6 +2117,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2141,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124176071</v>
+        <v>124175718</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,24 +2152,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2184,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461708</v>
+        <v>461713</v>
       </c>
       <c r="R15" t="n">
-        <v>6700899</v>
+        <v>6701043</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2247,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175776</v>
+        <v>124176373</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>92326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,30 +2258,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2294,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461720</v>
+        <v>461655</v>
       </c>
       <c r="R16" t="n">
-        <v>6701011</v>
+        <v>6700853</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2357,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175346</v>
+        <v>124175914</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,26 +2372,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2400,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461868</v>
+        <v>461694</v>
       </c>
       <c r="R17" t="n">
-        <v>6700927</v>
+        <v>6700999</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2444,7 +2456,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2463,7 +2474,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124174911</v>
+        <v>124175739</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2506,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461858</v>
+        <v>461713</v>
       </c>
       <c r="R18" t="n">
-        <v>6700851</v>
+        <v>6701035</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2569,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124174681</v>
+        <v>124174890</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,39 +2596,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2625,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461777</v>
+        <v>461855</v>
       </c>
       <c r="R19" t="n">
-        <v>6700942</v>
+        <v>6700846</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2669,6 +2667,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2687,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124174819</v>
+        <v>124175266</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,39 +2702,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2743,10 +2729,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461833</v>
+        <v>461917</v>
       </c>
       <c r="R20" t="n">
-        <v>6700849</v>
+        <v>6700885</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2787,6 +2773,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124175498</v>
+        <v>124175381</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,31 +2808,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2853,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461876</v>
+        <v>461839</v>
       </c>
       <c r="R21" t="n">
-        <v>6700933</v>
+        <v>6700986</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2891,17 +2873,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2920,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124175319</v>
+        <v>124175647</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,39 +2910,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2972,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461910</v>
+        <v>461689</v>
       </c>
       <c r="R22" t="n">
-        <v>6700899</v>
+        <v>6701105</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3016,7 +2994,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3035,7 +3012,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175075</v>
+        <v>124175534</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3070,7 +3047,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3087,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461846</v>
+        <v>461735</v>
       </c>
       <c r="R23" t="n">
-        <v>6700848</v>
+        <v>6701055</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3150,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124176373</v>
+        <v>124174932</v>
       </c>
       <c r="B24" t="n">
-        <v>92326</v>
+        <v>91457</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,32 +3139,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3197,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461655</v>
+        <v>461851</v>
       </c>
       <c r="R24" t="n">
-        <v>6700853</v>
+        <v>6700848</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3260,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124175215</v>
+        <v>124175319</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,30 +3245,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3303,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461931</v>
+        <v>461910</v>
       </c>
       <c r="R25" t="n">
-        <v>6700883</v>
+        <v>6700899</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3366,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124176021</v>
+        <v>124174707</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,26 +3364,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3409,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461747</v>
+        <v>461884</v>
       </c>
       <c r="R26" t="n">
-        <v>6700906</v>
+        <v>6700921</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3453,7 +3448,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3472,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175381</v>
+        <v>124175498</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3488,26 +3482,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3515,10 +3514,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461839</v>
+        <v>461876</v>
       </c>
       <c r="R27" t="n">
-        <v>6700986</v>
+        <v>6700933</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3553,13 +3552,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3578,10 +3581,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175050</v>
+        <v>124174819</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3590,39 +3593,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3630,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461862</v>
+        <v>461833</v>
       </c>
       <c r="R28" t="n">
-        <v>6700845</v>
+        <v>6700849</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3674,7 +3681,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3693,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124176290</v>
+        <v>124175215</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3705,39 +3711,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3745,10 +3742,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461688</v>
+        <v>461931</v>
       </c>
       <c r="R29" t="n">
-        <v>6700877</v>
+        <v>6700883</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3808,10 +3805,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175156</v>
+        <v>124174911</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3820,39 +3817,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3860,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461943</v>
+        <v>461858</v>
       </c>
       <c r="R30" t="n">
-        <v>6700846</v>
+        <v>6700851</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3923,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124176275</v>
+        <v>124176021</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,39 +3923,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3975,10 +3954,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461688</v>
+        <v>461747</v>
       </c>
       <c r="R31" t="n">
-        <v>6700885</v>
+        <v>6700906</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4038,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175534</v>
+        <v>124174681</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,39 +4029,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4090,10 +4073,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461735</v>
+        <v>461777</v>
       </c>
       <c r="R32" t="n">
-        <v>6701055</v>
+        <v>6700942</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4134,7 +4117,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4153,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124174890</v>
+        <v>124175587</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,26 +4151,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4196,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461855</v>
+        <v>461706</v>
       </c>
       <c r="R33" t="n">
-        <v>6700846</v>
+        <v>6701095</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4226,12 +4213,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,7 +4232,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4250,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175739</v>
+        <v>124176275</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,30 +4262,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461713</v>
+        <v>461688</v>
       </c>
       <c r="R34" t="n">
-        <v>6701035</v>
+        <v>6700885</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124176306</v>
+        <v>124176071</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461677</v>
+        <v>461708</v>
       </c>
       <c r="R2" t="n">
-        <v>6700883</v>
+        <v>6700899</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124175776</v>
+        <v>124176290</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461720</v>
+        <v>461688</v>
       </c>
       <c r="R3" t="n">
-        <v>6701011</v>
+        <v>6700877</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175959</v>
+        <v>124176170</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,39 +912,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461702</v>
+        <v>461712</v>
       </c>
       <c r="R4" t="n">
-        <v>6701001</v>
+        <v>6700887</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124176170</v>
+        <v>124175319</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,34 +1018,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461712</v>
+        <v>461910</v>
       </c>
       <c r="R5" t="n">
-        <v>6700887</v>
+        <v>6700899</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1128,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175453</v>
+        <v>124175498</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,39 +1133,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461792</v>
+        <v>461876</v>
       </c>
       <c r="R6" t="n">
-        <v>6700952</v>
+        <v>6700933</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1218,13 +1207,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1243,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175156</v>
+        <v>124175587</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,39 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461943</v>
+        <v>461706</v>
       </c>
       <c r="R7" t="n">
-        <v>6700846</v>
+        <v>6701095</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1325,12 +1314,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1333,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1358,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175075</v>
+        <v>124175718</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1363,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1410,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461846</v>
+        <v>461713</v>
       </c>
       <c r="R8" t="n">
-        <v>6700848</v>
+        <v>6701043</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1473,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124176290</v>
+        <v>124175215</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1473,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1525,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461688</v>
+        <v>461931</v>
       </c>
       <c r="R9" t="n">
-        <v>6700877</v>
+        <v>6700883</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1588,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124174869</v>
+        <v>124175647</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,30 +1579,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1631,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461848</v>
+        <v>461689</v>
       </c>
       <c r="R10" t="n">
-        <v>6700855</v>
+        <v>6701105</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1675,7 +1663,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124176071</v>
+        <v>124174681</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,26 +1697,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461708</v>
+        <v>461777</v>
       </c>
       <c r="R11" t="n">
-        <v>6700899</v>
+        <v>6700942</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1781,7 +1781,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175346</v>
+        <v>124175739</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1843,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461868</v>
+        <v>461713</v>
       </c>
       <c r="R12" t="n">
-        <v>6700927</v>
+        <v>6701035</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1906,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124175050</v>
+        <v>124176373</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>92326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,39 +1917,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1958,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461862</v>
+        <v>461655</v>
       </c>
       <c r="R13" t="n">
-        <v>6700845</v>
+        <v>6700853</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2021,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175111</v>
+        <v>124175914</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,39 +2027,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461897</v>
+        <v>461694</v>
       </c>
       <c r="R14" t="n">
-        <v>6700803</v>
+        <v>6700999</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2117,7 +2115,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175718</v>
+        <v>124174932</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,32 +2145,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2183,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461713</v>
+        <v>461851</v>
       </c>
       <c r="R15" t="n">
-        <v>6701043</v>
+        <v>6700848</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2246,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124176373</v>
+        <v>124175534</v>
       </c>
       <c r="B16" t="n">
-        <v>92326</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,34 +2251,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2293,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461655</v>
+        <v>461735</v>
       </c>
       <c r="R16" t="n">
-        <v>6700853</v>
+        <v>6701055</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2356,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175914</v>
+        <v>124175050</v>
       </c>
       <c r="B17" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,43 +2366,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2412,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461694</v>
+        <v>461862</v>
       </c>
       <c r="R17" t="n">
-        <v>6700999</v>
+        <v>6700845</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2456,6 +2450,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2474,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175739</v>
+        <v>124176021</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461713</v>
+        <v>461747</v>
       </c>
       <c r="R18" t="n">
-        <v>6701035</v>
+        <v>6700906</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124174890</v>
+        <v>124175266</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,21 +2591,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461855</v>
+        <v>461917</v>
       </c>
       <c r="R19" t="n">
-        <v>6700846</v>
+        <v>6700885</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2686,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175266</v>
+        <v>124175111</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,30 +2693,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2729,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461917</v>
+        <v>461897</v>
       </c>
       <c r="R20" t="n">
-        <v>6700885</v>
+        <v>6700803</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2792,7 +2796,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124175381</v>
+        <v>124175346</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2835,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461839</v>
+        <v>461868</v>
       </c>
       <c r="R21" t="n">
-        <v>6700986</v>
+        <v>6700927</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2898,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124175647</v>
+        <v>124176306</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,39 +2914,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2950,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461689</v>
+        <v>461677</v>
       </c>
       <c r="R22" t="n">
-        <v>6701105</v>
+        <v>6700883</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2994,6 +2998,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175534</v>
+        <v>124174819</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,39 +3029,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3064,10 +3073,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461735</v>
+        <v>461833</v>
       </c>
       <c r="R23" t="n">
-        <v>6701055</v>
+        <v>6700849</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3108,7 +3117,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3127,10 +3135,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124174932</v>
+        <v>124175156</v>
       </c>
       <c r="B24" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3143,26 +3151,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3170,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461851</v>
+        <v>461943</v>
       </c>
       <c r="R24" t="n">
-        <v>6700848</v>
+        <v>6700846</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3233,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124175319</v>
+        <v>124174890</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,39 +3262,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3285,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461910</v>
+        <v>461855</v>
       </c>
       <c r="R25" t="n">
-        <v>6700899</v>
+        <v>6700846</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3348,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124174707</v>
+        <v>124174869</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,39 +3372,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3404,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461884</v>
+        <v>461848</v>
       </c>
       <c r="R26" t="n">
-        <v>6700921</v>
+        <v>6700855</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3448,6 +3443,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3466,10 +3462,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175498</v>
+        <v>124175381</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3482,31 +3478,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3514,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461876</v>
+        <v>461839</v>
       </c>
       <c r="R27" t="n">
-        <v>6700933</v>
+        <v>6700986</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3552,17 +3543,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3581,7 +3568,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124174819</v>
+        <v>124174707</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3622,7 +3609,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3637,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461833</v>
+        <v>461884</v>
       </c>
       <c r="R28" t="n">
-        <v>6700849</v>
+        <v>6700921</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3699,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124175215</v>
+        <v>124176275</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,30 +3698,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3742,10 +3738,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461931</v>
+        <v>461688</v>
       </c>
       <c r="R29" t="n">
-        <v>6700883</v>
+        <v>6700885</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3805,10 +3801,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124174911</v>
+        <v>124175075</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3817,30 +3813,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461858</v>
+        <v>461846</v>
       </c>
       <c r="R30" t="n">
-        <v>6700851</v>
+        <v>6700848</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3911,10 +3916,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124176021</v>
+        <v>124175776</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3927,24 +3932,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3954,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461747</v>
+        <v>461720</v>
       </c>
       <c r="R31" t="n">
-        <v>6700906</v>
+        <v>6701011</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4017,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124174681</v>
+        <v>124175959</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>57519</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4033,16 +4042,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4058,7 +4067,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4073,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461777</v>
+        <v>461702</v>
       </c>
       <c r="R32" t="n">
-        <v>6700942</v>
+        <v>6701001</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4135,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175587</v>
+        <v>124175453</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4147,35 +4156,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4183,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461706</v>
+        <v>461792</v>
       </c>
       <c r="R33" t="n">
-        <v>6701095</v>
+        <v>6700952</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4213,17 +4226,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,6 +4240,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4250,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124176275</v>
+        <v>124174911</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4262,39 +4271,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461688</v>
+        <v>461858</v>
       </c>
       <c r="R34" t="n">
-        <v>6700885</v>
+        <v>6700851</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124176071</v>
+        <v>124176021</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461708</v>
+        <v>461747</v>
       </c>
       <c r="R2" t="n">
-        <v>6700899</v>
+        <v>6700906</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124176290</v>
+        <v>124174869</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461688</v>
+        <v>461848</v>
       </c>
       <c r="R3" t="n">
-        <v>6700877</v>
+        <v>6700855</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124176170</v>
+        <v>124174890</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,28 +903,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -943,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461712</v>
+        <v>461855</v>
       </c>
       <c r="R4" t="n">
-        <v>6700887</v>
+        <v>6700846</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175319</v>
+        <v>124176071</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,39 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,7 +1036,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461910</v>
+        <v>461708</v>
       </c>
       <c r="R5" t="n">
         <v>6700899</v>
@@ -1121,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175498</v>
+        <v>124176290</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,35 +1111,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461876</v>
+        <v>461688</v>
       </c>
       <c r="R6" t="n">
-        <v>6700933</v>
+        <v>6700877</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1207,17 +1189,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175587</v>
+        <v>124175959</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,16 +1230,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1269,12 +1247,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1284,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461706</v>
+        <v>461702</v>
       </c>
       <c r="R7" t="n">
-        <v>6701095</v>
+        <v>6701001</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,17 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175718</v>
+        <v>124175156</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1344,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461713</v>
+        <v>461943</v>
       </c>
       <c r="R8" t="n">
-        <v>6701043</v>
+        <v>6700846</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1461,7 +1447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124175215</v>
+        <v>124175346</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1504,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461931</v>
+        <v>461868</v>
       </c>
       <c r="R9" t="n">
-        <v>6700883</v>
+        <v>6700927</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124175647</v>
+        <v>124176170</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,39 +1565,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461689</v>
+        <v>461712</v>
       </c>
       <c r="R10" t="n">
-        <v>6701105</v>
+        <v>6700887</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1663,6 +1644,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124174681</v>
+        <v>124175534</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,43 +1675,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461777</v>
+        <v>461735</v>
       </c>
       <c r="R11" t="n">
-        <v>6700942</v>
+        <v>6701055</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1781,6 +1759,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1905,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124176373</v>
+        <v>124174707</v>
       </c>
       <c r="B13" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,34 +1896,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1952,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461655</v>
+        <v>461884</v>
       </c>
       <c r="R13" t="n">
-        <v>6700853</v>
+        <v>6700921</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1996,7 +1984,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2015,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175914</v>
+        <v>124175718</v>
       </c>
       <c r="B14" t="n">
-        <v>57519</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,21 +2018,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2053,17 +2040,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2071,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461694</v>
+        <v>461713</v>
       </c>
       <c r="R14" t="n">
-        <v>6700999</v>
+        <v>6701043</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2115,6 +2093,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2133,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124174932</v>
+        <v>124175215</v>
       </c>
       <c r="B15" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461851</v>
+        <v>461931</v>
       </c>
       <c r="R15" t="n">
-        <v>6700848</v>
+        <v>6700883</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2239,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175534</v>
+        <v>124176275</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2274,7 +2253,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2291,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461735</v>
+        <v>461688</v>
       </c>
       <c r="R16" t="n">
-        <v>6701055</v>
+        <v>6700885</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2354,7 +2333,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175050</v>
+        <v>124175319</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2389,7 +2368,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461862</v>
+        <v>461910</v>
       </c>
       <c r="R17" t="n">
-        <v>6700845</v>
+        <v>6700899</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2469,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124176021</v>
+        <v>124175050</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,30 +2460,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2512,10 +2500,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461747</v>
+        <v>461862</v>
       </c>
       <c r="R18" t="n">
-        <v>6700906</v>
+        <v>6700845</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2575,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175266</v>
+        <v>124176306</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,30 +2575,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2618,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461917</v>
+        <v>461677</v>
       </c>
       <c r="R19" t="n">
-        <v>6700885</v>
+        <v>6700883</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2681,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175111</v>
+        <v>124174911</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,39 +2690,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2733,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461897</v>
+        <v>461858</v>
       </c>
       <c r="R20" t="n">
-        <v>6700803</v>
+        <v>6700851</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2796,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124175346</v>
+        <v>124176373</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>92326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2808,28 +2796,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2839,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461868</v>
+        <v>461655</v>
       </c>
       <c r="R21" t="n">
-        <v>6700927</v>
+        <v>6700853</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2902,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124176306</v>
+        <v>124175647</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,39 +2906,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2954,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461677</v>
+        <v>461689</v>
       </c>
       <c r="R22" t="n">
-        <v>6700883</v>
+        <v>6701105</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2998,7 +2990,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3017,7 +3008,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124174819</v>
+        <v>124175587</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3050,20 +3041,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3073,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461833</v>
+        <v>461706</v>
       </c>
       <c r="R23" t="n">
-        <v>6700849</v>
+        <v>6701095</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3103,12 +3086,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124175156</v>
+        <v>124175381</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3147,39 +3135,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3187,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461943</v>
+        <v>461839</v>
       </c>
       <c r="R24" t="n">
-        <v>6700846</v>
+        <v>6700986</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3250,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124174890</v>
+        <v>124174681</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3266,26 +3245,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3293,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461855</v>
+        <v>461777</v>
       </c>
       <c r="R25" t="n">
-        <v>6700846</v>
+        <v>6700942</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3337,7 +3329,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124174869</v>
+        <v>124174819</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3372,26 +3363,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461848</v>
+        <v>461833</v>
       </c>
       <c r="R26" t="n">
-        <v>6700855</v>
+        <v>6700849</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3443,7 +3447,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3462,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175381</v>
+        <v>124175776</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3478,24 +3481,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3505,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461839</v>
+        <v>461720</v>
       </c>
       <c r="R27" t="n">
-        <v>6700986</v>
+        <v>6701011</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3568,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124174707</v>
+        <v>124175453</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3580,43 +3587,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3624,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461884</v>
+        <v>461792</v>
       </c>
       <c r="R28" t="n">
-        <v>6700921</v>
+        <v>6700952</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3668,6 +3671,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3686,10 +3690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124176275</v>
+        <v>124174932</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,35 +3706,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461688</v>
+        <v>461851</v>
       </c>
       <c r="R29" t="n">
-        <v>6700885</v>
+        <v>6700848</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3801,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175075</v>
+        <v>124175498</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3813,39 +3808,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3853,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461846</v>
+        <v>461876</v>
       </c>
       <c r="R30" t="n">
-        <v>6700848</v>
+        <v>6700933</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3891,13 +3882,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175776</v>
+        <v>124175075</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3928,34 +3923,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461720</v>
+        <v>461846</v>
       </c>
       <c r="R31" t="n">
-        <v>6701011</v>
+        <v>6700848</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175959</v>
+        <v>124175111</v>
       </c>
       <c r="B32" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4038,43 +4038,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4082,10 +4078,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461702</v>
+        <v>461897</v>
       </c>
       <c r="R32" t="n">
-        <v>6701001</v>
+        <v>6700803</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4126,6 +4122,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4144,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175453</v>
+        <v>124175914</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4156,39 +4153,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4196,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461792</v>
+        <v>461694</v>
       </c>
       <c r="R33" t="n">
-        <v>6700952</v>
+        <v>6700999</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4240,7 +4241,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124174911</v>
+        <v>124175266</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461858</v>
+        <v>461917</v>
       </c>
       <c r="R34" t="n">
-        <v>6700851</v>
+        <v>6700885</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124174890</v>
+        <v>124176290</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461855</v>
+        <v>461688</v>
       </c>
       <c r="R4" t="n">
-        <v>6700846</v>
+        <v>6700877</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124176071</v>
+        <v>124175959</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1018,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461708</v>
+        <v>461702</v>
       </c>
       <c r="R5" t="n">
-        <v>6700899</v>
+        <v>6701001</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1080,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124176290</v>
+        <v>124174890</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,39 +1132,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461688</v>
+        <v>461855</v>
       </c>
       <c r="R6" t="n">
-        <v>6700877</v>
+        <v>6700846</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1214,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175959</v>
+        <v>124176071</v>
       </c>
       <c r="B7" t="n">
-        <v>57519</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,39 +1242,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461702</v>
+        <v>461708</v>
       </c>
       <c r="R7" t="n">
-        <v>6701001</v>
+        <v>6700899</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1314,6 +1313,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175156</v>
+        <v>124175346</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,39 +1344,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461943</v>
+        <v>461868</v>
       </c>
       <c r="R8" t="n">
-        <v>6700846</v>
+        <v>6700927</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1447,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124175346</v>
+        <v>124176170</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,24 +1454,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1490,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461868</v>
+        <v>461712</v>
       </c>
       <c r="R9" t="n">
-        <v>6700927</v>
+        <v>6700887</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124176170</v>
+        <v>124175156</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,34 +1560,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461712</v>
+        <v>461943</v>
       </c>
       <c r="R10" t="n">
-        <v>6700887</v>
+        <v>6700846</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175534</v>
+        <v>124175739</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,39 +1675,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461735</v>
+        <v>461713</v>
       </c>
       <c r="R11" t="n">
-        <v>6701055</v>
+        <v>6701035</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1778,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175739</v>
+        <v>124175534</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,30 +1781,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461713</v>
+        <v>461735</v>
       </c>
       <c r="R12" t="n">
-        <v>6701035</v>
+        <v>6701055</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175914</v>
+        <v>124175266</v>
       </c>
       <c r="B33" t="n">
-        <v>57519</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,39 +4157,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4197,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461694</v>
+        <v>461917</v>
       </c>
       <c r="R33" t="n">
-        <v>6700999</v>
+        <v>6700885</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4241,6 +4228,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4247,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175266</v>
+        <v>124175914</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57519</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,26 +4263,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4303,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461917</v>
+        <v>461694</v>
       </c>
       <c r="R34" t="n">
-        <v>6700885</v>
+        <v>6700999</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4346,7 +4347,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124176021</v>
+        <v>124175647</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461747</v>
+        <v>461689</v>
       </c>
       <c r="R2" t="n">
-        <v>6700906</v>
+        <v>6701105</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124174869</v>
+        <v>124174707</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +805,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461848</v>
+        <v>461884</v>
       </c>
       <c r="R3" t="n">
-        <v>6700855</v>
+        <v>6700921</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,7 +889,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124176290</v>
+        <v>124175215</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +919,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461688</v>
+        <v>461931</v>
       </c>
       <c r="R4" t="n">
-        <v>6700877</v>
+        <v>6700883</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175959</v>
+        <v>124176021</v>
       </c>
       <c r="B5" t="n">
-        <v>57519</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,39 +1029,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461702</v>
+        <v>461747</v>
       </c>
       <c r="R5" t="n">
-        <v>6701001</v>
+        <v>6700906</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1102,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124174890</v>
+        <v>124174869</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1163,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461855</v>
+        <v>461848</v>
       </c>
       <c r="R6" t="n">
-        <v>6700846</v>
+        <v>6700855</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1226,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124176071</v>
+        <v>124175111</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,30 +1237,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461708</v>
+        <v>461897</v>
       </c>
       <c r="R7" t="n">
-        <v>6700899</v>
+        <v>6700803</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175346</v>
+        <v>124174911</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1375,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461868</v>
+        <v>461858</v>
       </c>
       <c r="R8" t="n">
-        <v>6700927</v>
+        <v>6700851</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1438,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124176170</v>
+        <v>124174819</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,30 +1462,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461712</v>
+        <v>461833</v>
       </c>
       <c r="R9" t="n">
-        <v>6700887</v>
+        <v>6700849</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1529,7 +1546,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124175156</v>
+        <v>124176306</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1583,7 +1599,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461943</v>
+        <v>461677</v>
       </c>
       <c r="R10" t="n">
-        <v>6700846</v>
+        <v>6700883</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1663,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175739</v>
+        <v>124175959</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,26 +1695,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461713</v>
+        <v>461702</v>
       </c>
       <c r="R11" t="n">
-        <v>6701035</v>
+        <v>6701001</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1750,7 +1779,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175534</v>
+        <v>124176275</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1804,7 +1832,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1821,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461735</v>
+        <v>461688</v>
       </c>
       <c r="R12" t="n">
-        <v>6701055</v>
+        <v>6700885</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1884,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124174707</v>
+        <v>124176290</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,43 +1924,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1940,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461884</v>
+        <v>461688</v>
       </c>
       <c r="R13" t="n">
-        <v>6700921</v>
+        <v>6700877</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1984,6 +2008,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175718</v>
+        <v>124174890</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,28 +2043,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2049,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461713</v>
+        <v>461855</v>
       </c>
       <c r="R14" t="n">
-        <v>6701043</v>
+        <v>6700846</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2112,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175215</v>
+        <v>124175914</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,26 +2149,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461931</v>
+        <v>461694</v>
       </c>
       <c r="R15" t="n">
-        <v>6700883</v>
+        <v>6700999</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2199,7 +2233,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2218,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124176275</v>
+        <v>124175534</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2253,7 +2286,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2270,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461688</v>
+        <v>461735</v>
       </c>
       <c r="R16" t="n">
-        <v>6700885</v>
+        <v>6701055</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2333,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175319</v>
+        <v>124176373</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>92326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,39 +2378,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2385,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461910</v>
+        <v>461655</v>
       </c>
       <c r="R17" t="n">
-        <v>6700899</v>
+        <v>6700853</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2448,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175050</v>
+        <v>124175266</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,39 +2488,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2500,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461862</v>
+        <v>461917</v>
       </c>
       <c r="R18" t="n">
-        <v>6700845</v>
+        <v>6700885</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2563,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124176306</v>
+        <v>124175498</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,39 +2594,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2615,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461677</v>
+        <v>461876</v>
       </c>
       <c r="R19" t="n">
-        <v>6700883</v>
+        <v>6700933</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2653,13 +2668,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2678,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124174911</v>
+        <v>124175156</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,30 +2709,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2721,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461858</v>
+        <v>461943</v>
       </c>
       <c r="R20" t="n">
-        <v>6700851</v>
+        <v>6700846</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2784,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124176373</v>
+        <v>124176170</v>
       </c>
       <c r="B21" t="n">
-        <v>92326</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,30 +2824,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2831,10 +2859,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461655</v>
+        <v>461712</v>
       </c>
       <c r="R21" t="n">
-        <v>6700853</v>
+        <v>6700887</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2894,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124175647</v>
+        <v>124174681</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2906,25 +2934,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2933,10 +2961,14 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2946,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461689</v>
+        <v>461777</v>
       </c>
       <c r="R22" t="n">
-        <v>6701105</v>
+        <v>6700942</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3008,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175587</v>
+        <v>124174932</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,35 +3052,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3056,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461706</v>
+        <v>461851</v>
       </c>
       <c r="R23" t="n">
-        <v>6701095</v>
+        <v>6700848</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3086,17 +3113,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,6 +3127,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3123,7 +3146,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124175381</v>
+        <v>124175739</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3166,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461839</v>
+        <v>461713</v>
       </c>
       <c r="R24" t="n">
-        <v>6700986</v>
+        <v>6701035</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3229,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124174681</v>
+        <v>124175718</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3267,17 +3290,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3285,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461777</v>
+        <v>461713</v>
       </c>
       <c r="R25" t="n">
-        <v>6700942</v>
+        <v>6701043</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3329,6 +3343,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3347,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124174819</v>
+        <v>124175346</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,39 +3378,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3403,10 +3405,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461833</v>
+        <v>461868</v>
       </c>
       <c r="R26" t="n">
-        <v>6700849</v>
+        <v>6700927</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3447,6 +3449,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3465,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175776</v>
+        <v>124175075</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,34 +3480,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3512,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461720</v>
+        <v>461846</v>
       </c>
       <c r="R27" t="n">
-        <v>6701011</v>
+        <v>6700848</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3575,7 +3583,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175453</v>
+        <v>124175050</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3610,7 +3618,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3627,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461792</v>
+        <v>461862</v>
       </c>
       <c r="R28" t="n">
-        <v>6700952</v>
+        <v>6700845</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3690,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124174932</v>
+        <v>124175381</v>
       </c>
       <c r="B29" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,25 +3710,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3733,10 +3741,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461851</v>
+        <v>461839</v>
       </c>
       <c r="R29" t="n">
-        <v>6700848</v>
+        <v>6700986</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3796,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175498</v>
+        <v>124175453</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,35 +3816,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3844,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461876</v>
+        <v>461792</v>
       </c>
       <c r="R30" t="n">
-        <v>6700933</v>
+        <v>6700952</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3882,17 +3894,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3911,10 +3919,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175075</v>
+        <v>124176071</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3923,39 +3931,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3963,10 +3962,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461846</v>
+        <v>461708</v>
       </c>
       <c r="R31" t="n">
-        <v>6700848</v>
+        <v>6700899</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4026,10 +4025,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175111</v>
+        <v>124175587</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4038,39 +4037,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4078,10 +4073,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461897</v>
+        <v>461706</v>
       </c>
       <c r="R32" t="n">
-        <v>6700803</v>
+        <v>6701095</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4108,12 +4103,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,7 +4122,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4141,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175266</v>
+        <v>124175776</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,24 +4156,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4184,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461917</v>
+        <v>461720</v>
       </c>
       <c r="R33" t="n">
-        <v>6700885</v>
+        <v>6701011</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4247,10 +4250,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175914</v>
+        <v>124175319</v>
       </c>
       <c r="B34" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4259,43 +4262,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4303,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461694</v>
+        <v>461910</v>
       </c>
       <c r="R34" t="n">
-        <v>6700999</v>
+        <v>6700899</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4347,6 +4346,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175914</v>
+        <v>124176373</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>92326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,43 +2145,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461694</v>
+        <v>461655</v>
       </c>
       <c r="R15" t="n">
-        <v>6700999</v>
+        <v>6700853</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2233,6 +2224,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175534</v>
+        <v>124175914</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,39 +2255,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2303,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461735</v>
+        <v>461694</v>
       </c>
       <c r="R16" t="n">
-        <v>6701055</v>
+        <v>6700999</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2347,7 +2343,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2366,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124176373</v>
+        <v>124175534</v>
       </c>
       <c r="B17" t="n">
-        <v>92326</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,34 +2373,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461655</v>
+        <v>461735</v>
       </c>
       <c r="R17" t="n">
-        <v>6700853</v>
+        <v>6701055</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175498</v>
+        <v>124175156</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,35 +2594,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2630,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461876</v>
+        <v>461943</v>
       </c>
       <c r="R19" t="n">
-        <v>6700933</v>
+        <v>6700846</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2668,17 +2672,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175156</v>
+        <v>124175498</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,39 +2709,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2749,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461943</v>
+        <v>461876</v>
       </c>
       <c r="R20" t="n">
-        <v>6700846</v>
+        <v>6700933</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2787,13 +2783,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175453</v>
+        <v>124176071</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,39 +3816,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3856,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461792</v>
+        <v>461708</v>
       </c>
       <c r="R30" t="n">
-        <v>6700952</v>
+        <v>6700899</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3919,10 +3910,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124176071</v>
+        <v>124175453</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3931,30 +3922,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461708</v>
+        <v>461792</v>
       </c>
       <c r="R31" t="n">
-        <v>6700899</v>
+        <v>6700952</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124174869</v>
+        <v>124174819</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1162,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461848</v>
+        <v>461833</v>
       </c>
       <c r="R6" t="n">
-        <v>6700855</v>
+        <v>6700849</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1206,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124174911</v>
+        <v>124174869</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461858</v>
+        <v>461848</v>
       </c>
       <c r="R8" t="n">
-        <v>6700851</v>
+        <v>6700855</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1446,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174819</v>
+        <v>124174911</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,39 +1474,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461833</v>
+        <v>461858</v>
       </c>
       <c r="R9" t="n">
-        <v>6700849</v>
+        <v>6700851</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1546,6 +1545,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124176290</v>
+        <v>124174890</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,39 +1924,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1964,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461688</v>
+        <v>461855</v>
       </c>
       <c r="R13" t="n">
-        <v>6700877</v>
+        <v>6700846</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2027,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124174890</v>
+        <v>124176290</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,30 +2030,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461855</v>
+        <v>461688</v>
       </c>
       <c r="R14" t="n">
-        <v>6700846</v>
+        <v>6700877</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124176373</v>
+        <v>124175914</v>
       </c>
       <c r="B15" t="n">
-        <v>92326</v>
+        <v>57519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,34 +2145,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2180,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461655</v>
+        <v>461694</v>
       </c>
       <c r="R15" t="n">
-        <v>6700853</v>
+        <v>6700999</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2224,7 +2233,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2243,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175914</v>
+        <v>124175534</v>
       </c>
       <c r="B16" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,43 +2263,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2299,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461694</v>
+        <v>461735</v>
       </c>
       <c r="R16" t="n">
-        <v>6700999</v>
+        <v>6701055</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2343,6 +2347,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2361,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124175534</v>
+        <v>124176373</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>92326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,39 +2378,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461735</v>
+        <v>461655</v>
       </c>
       <c r="R17" t="n">
-        <v>6701055</v>
+        <v>6700853</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175156</v>
+        <v>124175498</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,39 +2594,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2634,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461943</v>
+        <v>461876</v>
       </c>
       <c r="R19" t="n">
-        <v>6700846</v>
+        <v>6700933</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2672,13 +2668,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175498</v>
+        <v>124175156</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,35 +2709,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2745,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461876</v>
+        <v>461943</v>
       </c>
       <c r="R20" t="n">
-        <v>6700933</v>
+        <v>6700846</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2783,17 +2787,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124175346</v>
+        <v>124175075</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,30 +3374,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3405,10 +3414,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461868</v>
+        <v>461846</v>
       </c>
       <c r="R26" t="n">
-        <v>6700927</v>
+        <v>6700848</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3468,7 +3477,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175075</v>
+        <v>124175050</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3503,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3520,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461846</v>
+        <v>461862</v>
       </c>
       <c r="R27" t="n">
-        <v>6700848</v>
+        <v>6700845</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3583,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175050</v>
+        <v>124175346</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,39 +3604,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461862</v>
+        <v>461868</v>
       </c>
       <c r="R28" t="n">
-        <v>6700845</v>
+        <v>6700927</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124176071</v>
+        <v>124175453</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,30 +3816,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3847,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461708</v>
+        <v>461792</v>
       </c>
       <c r="R30" t="n">
-        <v>6700899</v>
+        <v>6700952</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3910,10 +3919,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175453</v>
+        <v>124176071</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3922,39 +3931,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461792</v>
+        <v>461708</v>
       </c>
       <c r="R31" t="n">
-        <v>6700952</v>
+        <v>6700899</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175647</v>
+        <v>124175075</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461689</v>
+        <v>461846</v>
       </c>
       <c r="R2" t="n">
-        <v>6701105</v>
+        <v>6700848</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124174707</v>
+        <v>124175319</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,43 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461884</v>
+        <v>461910</v>
       </c>
       <c r="R3" t="n">
-        <v>6700921</v>
+        <v>6700899</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175215</v>
+        <v>124175111</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461931</v>
+        <v>461897</v>
       </c>
       <c r="R4" t="n">
-        <v>6700883</v>
+        <v>6700803</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1013,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124176021</v>
+        <v>124175346</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1056,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461747</v>
+        <v>461868</v>
       </c>
       <c r="R5" t="n">
-        <v>6700906</v>
+        <v>6700927</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124174819</v>
+        <v>124176071</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1142,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461833</v>
+        <v>461708</v>
       </c>
       <c r="R6" t="n">
-        <v>6700849</v>
+        <v>6700899</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1219,6 +1213,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175111</v>
+        <v>124175587</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,39 +1244,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461897</v>
+        <v>461706</v>
       </c>
       <c r="R7" t="n">
-        <v>6700803</v>
+        <v>6701095</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,12 +1310,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124174869</v>
+        <v>124175647</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,30 +1359,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461848</v>
+        <v>461689</v>
       </c>
       <c r="R8" t="n">
-        <v>6700855</v>
+        <v>6701105</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1439,7 +1443,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174911</v>
+        <v>124175381</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1501,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461858</v>
+        <v>461839</v>
       </c>
       <c r="R9" t="n">
-        <v>6700851</v>
+        <v>6700986</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1564,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124176306</v>
+        <v>124176021</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,39 +1579,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461677</v>
+        <v>461747</v>
       </c>
       <c r="R10" t="n">
-        <v>6700883</v>
+        <v>6700906</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1679,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175959</v>
+        <v>124175453</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,43 +1685,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461702</v>
+        <v>461792</v>
       </c>
       <c r="R11" t="n">
-        <v>6701001</v>
+        <v>6700952</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1779,6 +1769,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1912,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124174890</v>
+        <v>124175739</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461855</v>
+        <v>461713</v>
       </c>
       <c r="R13" t="n">
-        <v>6700846</v>
+        <v>6701035</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2018,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124176290</v>
+        <v>124176170</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,39 +2021,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2070,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461688</v>
+        <v>461712</v>
       </c>
       <c r="R14" t="n">
-        <v>6700877</v>
+        <v>6700887</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2133,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175914</v>
+        <v>124176290</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,43 +2131,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461694</v>
+        <v>461688</v>
       </c>
       <c r="R15" t="n">
-        <v>6700999</v>
+        <v>6700877</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2233,6 +2215,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,7 +2234,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175534</v>
+        <v>124175050</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2286,7 +2269,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2303,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461735</v>
+        <v>461862</v>
       </c>
       <c r="R16" t="n">
-        <v>6701055</v>
+        <v>6700845</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2366,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124176373</v>
+        <v>124176306</v>
       </c>
       <c r="B17" t="n">
-        <v>92326</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,34 +2361,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2413,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461655</v>
+        <v>461677</v>
       </c>
       <c r="R17" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2476,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175266</v>
+        <v>124175914</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,26 +2480,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2519,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461917</v>
+        <v>461694</v>
       </c>
       <c r="R18" t="n">
-        <v>6700885</v>
+        <v>6700999</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2563,7 +2564,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175498</v>
+        <v>124175156</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,35 +2594,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2630,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461876</v>
+        <v>461943</v>
       </c>
       <c r="R19" t="n">
-        <v>6700933</v>
+        <v>6700846</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2668,17 +2672,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175156</v>
+        <v>124175776</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,39 +2709,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2749,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461943</v>
+        <v>461720</v>
       </c>
       <c r="R20" t="n">
-        <v>6700846</v>
+        <v>6701011</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2812,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124176170</v>
+        <v>124174819</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,30 +2823,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2859,10 +2863,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461712</v>
+        <v>461833</v>
       </c>
       <c r="R21" t="n">
-        <v>6700887</v>
+        <v>6700849</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2903,7 +2907,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2922,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124174681</v>
+        <v>124174890</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,39 +2941,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2978,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461777</v>
+        <v>461855</v>
       </c>
       <c r="R22" t="n">
-        <v>6700942</v>
+        <v>6700846</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3022,6 +3012,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3040,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124174932</v>
+        <v>124174911</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,25 +3043,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3083,10 +3074,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461851</v>
+        <v>461858</v>
       </c>
       <c r="R23" t="n">
-        <v>6700848</v>
+        <v>6700851</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3146,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124175739</v>
+        <v>124176373</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>92326</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3158,28 +3149,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3189,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461713</v>
+        <v>461655</v>
       </c>
       <c r="R24" t="n">
-        <v>6701035</v>
+        <v>6700853</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3252,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124175718</v>
+        <v>124174681</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,21 +3263,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3290,8 +3285,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3299,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461713</v>
+        <v>461777</v>
       </c>
       <c r="R25" t="n">
-        <v>6701043</v>
+        <v>6700942</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3343,7 +3347,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124175075</v>
+        <v>124175498</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,39 +3377,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3414,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461846</v>
+        <v>461876</v>
       </c>
       <c r="R26" t="n">
-        <v>6700848</v>
+        <v>6700933</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3452,13 +3451,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3477,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175050</v>
+        <v>124175266</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,39 +3492,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3529,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461862</v>
+        <v>461917</v>
       </c>
       <c r="R27" t="n">
-        <v>6700845</v>
+        <v>6700885</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3592,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175346</v>
+        <v>124175718</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,24 +3602,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3635,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461868</v>
+        <v>461713</v>
       </c>
       <c r="R28" t="n">
-        <v>6700927</v>
+        <v>6701043</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3698,10 +3696,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124175381</v>
+        <v>124174932</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3710,25 +3708,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3741,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461839</v>
+        <v>461851</v>
       </c>
       <c r="R29" t="n">
-        <v>6700986</v>
+        <v>6700848</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3804,10 +3802,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175453</v>
+        <v>124175959</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,39 +3814,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3856,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461792</v>
+        <v>461702</v>
       </c>
       <c r="R30" t="n">
-        <v>6700952</v>
+        <v>6701001</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3900,7 +3902,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3919,10 +3920,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124176071</v>
+        <v>124174707</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,26 +3936,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3962,10 +3976,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461708</v>
+        <v>461884</v>
       </c>
       <c r="R31" t="n">
-        <v>6700899</v>
+        <v>6700921</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4006,7 +4020,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4025,10 +4038,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175587</v>
+        <v>124175534</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4037,35 +4050,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4073,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461706</v>
+        <v>461735</v>
       </c>
       <c r="R32" t="n">
-        <v>6701095</v>
+        <v>6701055</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4103,17 +4120,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,6 +4134,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4140,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175776</v>
+        <v>124175215</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4156,28 +4169,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461720</v>
+        <v>461931</v>
       </c>
       <c r="R33" t="n">
-        <v>6701011</v>
+        <v>6700883</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4250,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175319</v>
+        <v>124174869</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4262,39 +4271,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461910</v>
+        <v>461848</v>
       </c>
       <c r="R34" t="n">
-        <v>6700899</v>
+        <v>6700855</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175075</v>
+        <v>124175111</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461846</v>
+        <v>461897</v>
       </c>
       <c r="R2" t="n">
-        <v>6700848</v>
+        <v>6700803</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124175319</v>
+        <v>124174932</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461910</v>
+        <v>461851</v>
       </c>
       <c r="R3" t="n">
-        <v>6700899</v>
+        <v>6700848</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -905,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175111</v>
+        <v>124175959</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +908,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461897</v>
+        <v>461702</v>
       </c>
       <c r="R4" t="n">
-        <v>6700803</v>
+        <v>6701001</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175346</v>
+        <v>124175498</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,26 +1030,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461868</v>
+        <v>461876</v>
       </c>
       <c r="R5" t="n">
-        <v>6700927</v>
+        <v>6700933</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1101,13 +1100,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124176071</v>
+        <v>124175587</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,26 +1145,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461708</v>
+        <v>461706</v>
       </c>
       <c r="R6" t="n">
-        <v>6700899</v>
+        <v>6701095</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1199,12 +1207,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1226,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175587</v>
+        <v>124176275</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,35 +1256,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461706</v>
+        <v>461688</v>
       </c>
       <c r="R7" t="n">
-        <v>6701095</v>
+        <v>6700885</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1310,17 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,6 +1340,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175647</v>
+        <v>124175346</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,39 +1371,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461689</v>
+        <v>461868</v>
       </c>
       <c r="R8" t="n">
-        <v>6701105</v>
+        <v>6700927</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1443,6 +1446,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124175381</v>
+        <v>124174869</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1481,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461839</v>
+        <v>461848</v>
       </c>
       <c r="R9" t="n">
-        <v>6700986</v>
+        <v>6700855</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124176021</v>
+        <v>124175453</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,30 +1583,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461747</v>
+        <v>461792</v>
       </c>
       <c r="R10" t="n">
-        <v>6700906</v>
+        <v>6700952</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1673,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175453</v>
+        <v>124176021</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,39 +1698,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1725,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461792</v>
+        <v>461747</v>
       </c>
       <c r="R11" t="n">
-        <v>6700952</v>
+        <v>6700906</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1788,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124176275</v>
+        <v>124175266</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,39 +1804,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,7 +1835,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461688</v>
+        <v>461917</v>
       </c>
       <c r="R12" t="n">
         <v>6700885</v>
@@ -1903,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124175739</v>
+        <v>124174681</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,26 +1914,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1946,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461713</v>
+        <v>461777</v>
       </c>
       <c r="R13" t="n">
-        <v>6701035</v>
+        <v>6700942</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1990,7 +1998,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2009,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124176170</v>
+        <v>124175739</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,28 +2032,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2056,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461712</v>
+        <v>461713</v>
       </c>
       <c r="R14" t="n">
-        <v>6700887</v>
+        <v>6701035</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2119,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124176290</v>
+        <v>124174707</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,39 +2134,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2171,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461688</v>
+        <v>461884</v>
       </c>
       <c r="R15" t="n">
-        <v>6700877</v>
+        <v>6700921</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2215,7 +2222,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2234,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175050</v>
+        <v>124175914</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,39 +2252,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2286,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461862</v>
+        <v>461694</v>
       </c>
       <c r="R16" t="n">
-        <v>6700845</v>
+        <v>6700999</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2330,7 +2340,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124176306</v>
+        <v>124176373</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>92326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,39 +2370,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2401,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461677</v>
+        <v>461655</v>
       </c>
       <c r="R17" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2464,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175914</v>
+        <v>124175718</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,21 +2484,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2502,17 +2506,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2520,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461694</v>
+        <v>461713</v>
       </c>
       <c r="R18" t="n">
-        <v>6700999</v>
+        <v>6701043</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2564,6 +2559,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2582,7 +2578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175156</v>
+        <v>124175050</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2617,7 +2613,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2634,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461943</v>
+        <v>461862</v>
       </c>
       <c r="R19" t="n">
-        <v>6700846</v>
+        <v>6700845</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2697,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175776</v>
+        <v>124175075</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,34 +2705,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2744,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461720</v>
+        <v>461846</v>
       </c>
       <c r="R20" t="n">
-        <v>6701011</v>
+        <v>6700848</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2807,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124174819</v>
+        <v>124175215</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,39 +2824,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2863,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461833</v>
+        <v>461931</v>
       </c>
       <c r="R21" t="n">
-        <v>6700849</v>
+        <v>6700883</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2907,6 +2895,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2914,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124174890</v>
+        <v>124176071</v>
       </c>
       <c r="B22" t="n">
         <v>91012</v>
@@ -2968,10 +2957,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461855</v>
+        <v>461708</v>
       </c>
       <c r="R22" t="n">
-        <v>6700846</v>
+        <v>6700899</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3137,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124176373</v>
+        <v>124175381</v>
       </c>
       <c r="B24" t="n">
-        <v>92326</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,32 +3138,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3184,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461655</v>
+        <v>461839</v>
       </c>
       <c r="R24" t="n">
-        <v>6700853</v>
+        <v>6700986</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3247,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124174681</v>
+        <v>124176170</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,39 +3248,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3303,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461777</v>
+        <v>461712</v>
       </c>
       <c r="R25" t="n">
-        <v>6700942</v>
+        <v>6700887</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3347,6 +3323,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3365,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124175498</v>
+        <v>124176290</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,35 +3354,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3413,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461876</v>
+        <v>461688</v>
       </c>
       <c r="R26" t="n">
-        <v>6700933</v>
+        <v>6700877</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3451,17 +3432,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3480,10 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175266</v>
+        <v>124175647</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3492,30 +3469,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3523,10 +3509,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461917</v>
+        <v>461689</v>
       </c>
       <c r="R27" t="n">
-        <v>6700885</v>
+        <v>6701105</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3567,7 +3553,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3586,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175718</v>
+        <v>124175319</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3598,34 +3583,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3633,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461713</v>
+        <v>461910</v>
       </c>
       <c r="R28" t="n">
-        <v>6701043</v>
+        <v>6700899</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3696,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124174932</v>
+        <v>124175534</v>
       </c>
       <c r="B29" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3712,26 +3702,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3739,10 +3738,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461851</v>
+        <v>461735</v>
       </c>
       <c r="R29" t="n">
-        <v>6700848</v>
+        <v>6701055</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3802,10 +3801,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124175959</v>
+        <v>124174890</v>
       </c>
       <c r="B30" t="n">
-        <v>57519</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3818,39 +3817,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3858,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461702</v>
+        <v>461855</v>
       </c>
       <c r="R30" t="n">
-        <v>6701001</v>
+        <v>6700846</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3902,6 +3888,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3920,10 +3907,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124174707</v>
+        <v>124175776</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3936,21 +3923,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3958,17 +3945,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3976,10 +3954,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461884</v>
+        <v>461720</v>
       </c>
       <c r="R31" t="n">
-        <v>6700921</v>
+        <v>6701011</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4020,6 +3998,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4038,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175534</v>
+        <v>124174819</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,39 +4029,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4090,10 +4073,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461735</v>
+        <v>461833</v>
       </c>
       <c r="R32" t="n">
-        <v>6701055</v>
+        <v>6700849</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4134,7 +4117,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4153,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175215</v>
+        <v>124175156</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4165,30 +4147,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4196,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461931</v>
+        <v>461943</v>
       </c>
       <c r="R33" t="n">
-        <v>6700883</v>
+        <v>6700846</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4259,10 +4250,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124174869</v>
+        <v>124176306</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,30 +4262,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461848</v>
+        <v>461677</v>
       </c>
       <c r="R34" t="n">
-        <v>6700855</v>
+        <v>6700883</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124176021</v>
+        <v>124175266</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461747</v>
+        <v>461917</v>
       </c>
       <c r="R11" t="n">
-        <v>6700906</v>
+        <v>6700885</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175266</v>
+        <v>124176021</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461917</v>
+        <v>461747</v>
       </c>
       <c r="R12" t="n">
-        <v>6700885</v>
+        <v>6700906</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124175739</v>
+        <v>124174707</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,26 +2032,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2059,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461713</v>
+        <v>461884</v>
       </c>
       <c r="R14" t="n">
-        <v>6701035</v>
+        <v>6700921</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2103,7 +2116,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2122,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124174707</v>
+        <v>124175739</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,39 +2150,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461884</v>
+        <v>461713</v>
       </c>
       <c r="R15" t="n">
-        <v>6700921</v>
+        <v>6701035</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2222,6 +2221,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124175215</v>
+        <v>124176071</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461931</v>
+        <v>461708</v>
       </c>
       <c r="R21" t="n">
-        <v>6700883</v>
+        <v>6700899</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124176071</v>
+        <v>124174911</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461708</v>
+        <v>461858</v>
       </c>
       <c r="R22" t="n">
-        <v>6700899</v>
+        <v>6700851</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124174911</v>
+        <v>124175215</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461858</v>
+        <v>461931</v>
       </c>
       <c r="R23" t="n">
-        <v>6700851</v>
+        <v>6700883</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175111</v>
+        <v>124175534</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461897</v>
+        <v>461735</v>
       </c>
       <c r="R2" t="n">
-        <v>6700803</v>
+        <v>6701055</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124174932</v>
+        <v>124176275</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +806,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461851</v>
+        <v>461688</v>
       </c>
       <c r="R3" t="n">
-        <v>6700848</v>
+        <v>6700885</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175959</v>
+        <v>124175914</v>
       </c>
       <c r="B4" t="n">
         <v>57519</v>
@@ -937,7 +946,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -952,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461702</v>
+        <v>461694</v>
       </c>
       <c r="R4" t="n">
-        <v>6701001</v>
+        <v>6700999</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1014,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175498</v>
+        <v>124175266</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461876</v>
+        <v>461917</v>
       </c>
       <c r="R5" t="n">
-        <v>6700933</v>
+        <v>6700885</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1100,17 +1104,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175587</v>
+        <v>124175498</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1167,7 +1167,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461706</v>
+        <v>461876</v>
       </c>
       <c r="R6" t="n">
-        <v>6701095</v>
+        <v>6700933</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124176275</v>
+        <v>124175453</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461688</v>
+        <v>461792</v>
       </c>
       <c r="R7" t="n">
-        <v>6700885</v>
+        <v>6700952</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175346</v>
+        <v>124175111</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,30 +1371,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461868</v>
+        <v>461897</v>
       </c>
       <c r="R8" t="n">
-        <v>6700927</v>
+        <v>6700803</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1465,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124174869</v>
+        <v>124175718</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,24 +1490,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1508,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461848</v>
+        <v>461713</v>
       </c>
       <c r="R9" t="n">
-        <v>6700855</v>
+        <v>6701043</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1571,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124175453</v>
+        <v>124175647</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,39 +1596,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461792</v>
+        <v>461689</v>
       </c>
       <c r="R10" t="n">
-        <v>6700952</v>
+        <v>6701105</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1667,7 +1680,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175266</v>
+        <v>124175776</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,24 +1714,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1729,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461917</v>
+        <v>461720</v>
       </c>
       <c r="R11" t="n">
-        <v>6700885</v>
+        <v>6701011</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1792,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124176021</v>
+        <v>124174911</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1835,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461747</v>
+        <v>461858</v>
       </c>
       <c r="R12" t="n">
-        <v>6700906</v>
+        <v>6700851</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1898,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124174681</v>
+        <v>124175215</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,39 +1930,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1954,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461777</v>
+        <v>461931</v>
       </c>
       <c r="R13" t="n">
-        <v>6700942</v>
+        <v>6700883</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1998,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2016,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124174707</v>
+        <v>124176373</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,43 +2032,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461884</v>
+        <v>461655</v>
       </c>
       <c r="R14" t="n">
-        <v>6700921</v>
+        <v>6700853</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2116,6 +2111,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2134,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124175739</v>
+        <v>124174869</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461713</v>
+        <v>461848</v>
       </c>
       <c r="R15" t="n">
-        <v>6701035</v>
+        <v>6700855</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2240,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124175914</v>
+        <v>124174681</v>
       </c>
       <c r="B16" t="n">
-        <v>57519</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,16 +2252,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2296,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461694</v>
+        <v>461777</v>
       </c>
       <c r="R16" t="n">
-        <v>6700999</v>
+        <v>6700942</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2358,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124176373</v>
+        <v>124176290</v>
       </c>
       <c r="B17" t="n">
-        <v>92326</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,25 +2366,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2396,8 +2392,13 @@
           <t>15</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2405,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461655</v>
+        <v>461688</v>
       </c>
       <c r="R17" t="n">
-        <v>6700853</v>
+        <v>6700877</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2468,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175718</v>
+        <v>124175959</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2506,8 +2507,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2515,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461713</v>
+        <v>461702</v>
       </c>
       <c r="R18" t="n">
-        <v>6701043</v>
+        <v>6701001</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2559,7 +2569,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2578,7 +2587,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175050</v>
+        <v>124175156</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2613,7 +2622,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2630,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461862</v>
+        <v>461943</v>
       </c>
       <c r="R19" t="n">
-        <v>6700845</v>
+        <v>6700846</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2693,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175075</v>
+        <v>124175587</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,39 +2714,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2745,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461846</v>
+        <v>461706</v>
       </c>
       <c r="R20" t="n">
-        <v>6700848</v>
+        <v>6701095</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2775,12 +2780,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,7 +2799,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2808,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124176071</v>
+        <v>124174819</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,26 +2833,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2851,10 +2873,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461708</v>
+        <v>461833</v>
       </c>
       <c r="R21" t="n">
-        <v>6700899</v>
+        <v>6700849</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2895,7 +2917,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2914,7 +2935,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124174911</v>
+        <v>124175346</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2957,10 +2978,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461858</v>
+        <v>461868</v>
       </c>
       <c r="R22" t="n">
-        <v>6700851</v>
+        <v>6700927</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3020,7 +3041,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175215</v>
+        <v>124175739</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3063,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461931</v>
+        <v>461713</v>
       </c>
       <c r="R23" t="n">
-        <v>6700883</v>
+        <v>6701035</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3126,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124175381</v>
+        <v>124176170</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3142,24 +3163,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3169,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461839</v>
+        <v>461712</v>
       </c>
       <c r="R24" t="n">
-        <v>6700986</v>
+        <v>6700887</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3232,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124176170</v>
+        <v>124176071</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3248,28 +3273,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3279,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461712</v>
+        <v>461708</v>
       </c>
       <c r="R25" t="n">
-        <v>6700887</v>
+        <v>6700899</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3342,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124176290</v>
+        <v>124174932</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3358,35 +3379,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3394,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461688</v>
+        <v>461851</v>
       </c>
       <c r="R26" t="n">
-        <v>6700877</v>
+        <v>6700848</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3457,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124175647</v>
+        <v>124176021</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3469,39 +3481,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3509,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461689</v>
+        <v>461747</v>
       </c>
       <c r="R27" t="n">
-        <v>6701105</v>
+        <v>6700906</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3553,6 +3556,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3571,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175319</v>
+        <v>124175381</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,39 +3587,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3623,10 +3618,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461910</v>
+        <v>461839</v>
       </c>
       <c r="R28" t="n">
-        <v>6700899</v>
+        <v>6700986</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3686,7 +3681,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124175534</v>
+        <v>124175075</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3721,7 +3716,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461735</v>
+        <v>461846</v>
       </c>
       <c r="R29" t="n">
-        <v>6701055</v>
+        <v>6700848</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3801,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124174890</v>
+        <v>124176306</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3813,30 +3808,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3844,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461855</v>
+        <v>461677</v>
       </c>
       <c r="R30" t="n">
-        <v>6700846</v>
+        <v>6700883</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3907,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124175776</v>
+        <v>124174707</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3923,21 +3927,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3945,8 +3949,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3954,10 +3967,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461720</v>
+        <v>461884</v>
       </c>
       <c r="R31" t="n">
-        <v>6701011</v>
+        <v>6700921</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3998,7 +4011,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4017,10 +4029,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124174819</v>
+        <v>124175319</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4029,43 +4041,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4073,10 +4081,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461833</v>
+        <v>461910</v>
       </c>
       <c r="R32" t="n">
-        <v>6700849</v>
+        <v>6700899</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4117,6 +4125,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4135,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124175156</v>
+        <v>124174890</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4147,39 +4156,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461943</v>
+        <v>461855</v>
       </c>
       <c r="R33" t="n">
         <v>6700846</v>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124176306</v>
+        <v>124175050</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461677</v>
+        <v>461862</v>
       </c>
       <c r="R34" t="n">
-        <v>6700883</v>
+        <v>6700845</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175266</v>
+        <v>124175453</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1035,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461917</v>
+        <v>461792</v>
       </c>
       <c r="R5" t="n">
-        <v>6700885</v>
+        <v>6700952</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1129,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175498</v>
+        <v>124175266</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,31 +1154,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461876</v>
+        <v>461917</v>
       </c>
       <c r="R6" t="n">
-        <v>6700933</v>
+        <v>6700885</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,17 +1219,13 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175453</v>
+        <v>124175498</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1296,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461792</v>
+        <v>461876</v>
       </c>
       <c r="R7" t="n">
-        <v>6700952</v>
+        <v>6700933</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1334,13 +1330,17 @@
           <t>2025-04-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124175776</v>
+        <v>124174911</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,28 +1714,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1745,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461720</v>
+        <v>461858</v>
       </c>
       <c r="R11" t="n">
-        <v>6701011</v>
+        <v>6700851</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1808,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124174911</v>
+        <v>124175776</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,24 +1820,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461858</v>
+        <v>461720</v>
       </c>
       <c r="R12" t="n">
-        <v>6700851</v>
+        <v>6701011</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124176170</v>
+        <v>124176071</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3163,28 +3163,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3194,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461712</v>
+        <v>461708</v>
       </c>
       <c r="R24" t="n">
-        <v>6700887</v>
+        <v>6700899</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3257,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124176071</v>
+        <v>124174932</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,25 +3265,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461708</v>
+        <v>461851</v>
       </c>
       <c r="R25" t="n">
-        <v>6700899</v>
+        <v>6700848</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3363,10 +3359,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124174932</v>
+        <v>124176021</v>
       </c>
       <c r="B26" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3371,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3406,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461851</v>
+        <v>461747</v>
       </c>
       <c r="R26" t="n">
-        <v>6700848</v>
+        <v>6700906</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3469,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124176021</v>
+        <v>124176170</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,24 +3481,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461747</v>
+        <v>461712</v>
       </c>
       <c r="R27" t="n">
-        <v>6700906</v>
+        <v>6700887</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4363,6 +4363,3381 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129386134</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>461791</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6700853</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129386049</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>461823</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6700883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129386181</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>461809</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6700924</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129386082</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>461838</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6700865</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129386074</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>461874</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6700850</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129385966</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98704</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>461831</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6700895</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129385719</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>461960</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6700956</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129386552</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>461718</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6700893</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bohål i döende gran, angripen av granticka. 2st 4-5 cm runda bohål, 2,5 meter upp på stammen.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129386264</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92257</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>461718</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6701058</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129385867</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>461920</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6700812</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129385788</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>461925</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6700914</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129386306</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>461691</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6700983</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129385753</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>461960</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6700969</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129385684</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>461868</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6700949</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129386233</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>461767</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6700964</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129386716</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>461581</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6700899</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129386225</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>461776</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6700968</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129386256</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>461731</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6701017</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129385780</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>461935</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6700926</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129386288</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98704</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>461678</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6700995</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129385669</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>461858</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6700997</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129385794</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>461932</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6700907</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129386272</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>461685</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6701059</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129386187</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>461816</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6700916</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129385764</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>461972</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6700967</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129386062</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>461861</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6700879</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129385673</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>461869</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6700980</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129385729</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>461948</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6700980</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129385644</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>461812</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6700990</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129385937</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>461930</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6700825</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129386570</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98704</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>461630</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6700920</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129386729</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>461658</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6700848</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4466,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,42 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,17 +4872,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4906,46 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4953,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4991,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5016,37 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>91504</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5227,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B43" t="n">
-        <v>92257</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R43" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5438,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385788</v>
+        <v>129386264</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461925</v>
+        <v>461718</v>
       </c>
       <c r="R45" t="n">
-        <v>6700914</v>
+        <v>6701058</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5542,7 +5542,7 @@
         <v>129386306</v>
       </c>
       <c r="B46" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5559,14 +5559,10 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5640,7 +5636,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385753</v>
+        <v>129385788</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5678,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461960</v>
+        <v>461925</v>
       </c>
       <c r="R47" t="n">
-        <v>6700969</v>
+        <v>6700914</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5741,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385684</v>
+        <v>129385753</v>
       </c>
       <c r="B48" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,21 +5748,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5779,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461868</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6700949</v>
+        <v>6700969</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6374,46 +6370,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129386288</v>
+        <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6421,10 +6408,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461678</v>
+        <v>461858</v>
       </c>
       <c r="R54" t="n">
-        <v>6700995</v>
+        <v>6700997</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6484,37 +6471,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129385669</v>
+        <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6522,10 +6518,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461858</v>
+        <v>461678</v>
       </c>
       <c r="R55" t="n">
-        <v>6700997</v>
+        <v>6700995</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6585,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6596,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6623,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6686,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6724,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6787,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>91504</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6825,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7524,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7634,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385684</v>
+        <v>129385788</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,21 +5238,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461868</v>
+        <v>461925</v>
       </c>
       <c r="R43" t="n">
-        <v>6700949</v>
+        <v>6700914</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385867</v>
+        <v>129385753</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,31 +5339,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461920</v>
+        <v>461960</v>
       </c>
       <c r="R44" t="n">
-        <v>6700812</v>
+        <v>6700969</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5409,17 +5404,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5438,32 +5429,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B45" t="n">
-        <v>92258</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5476,10 +5467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R45" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5539,30 +5530,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386306</v>
+        <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>92258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461691</v>
+        <v>461718</v>
       </c>
       <c r="R46" t="n">
-        <v>6700983</v>
+        <v>6701058</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,10 +5631,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,26 +5642,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R47" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,13 +5712,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,10 +5741,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5748,23 +5752,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R48" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4588,7 +4588,7 @@
         <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385788</v>
+        <v>129386306</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,23 +5238,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -5265,10 +5261,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461925</v>
+        <v>461691</v>
       </c>
       <c r="R43" t="n">
-        <v>6700914</v>
+        <v>6700983</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,10 +5324,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385753</v>
+        <v>129385867</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,26 +5335,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5366,10 +5367,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461960</v>
+        <v>461920</v>
       </c>
       <c r="R44" t="n">
-        <v>6700969</v>
+        <v>6700812</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5404,13 +5405,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5432,7 +5437,7 @@
         <v>129385684</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5533,7 +5538,7 @@
         <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385867</v>
+        <v>129385788</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5642,31 +5647,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461920</v>
+        <v>461925</v>
       </c>
       <c r="R47" t="n">
-        <v>6700812</v>
+        <v>6700914</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,17 +5712,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5741,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B48" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,19 +5748,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>91504</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R58" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6887,7 +6887,7 @@
         <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129385673</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385729</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -5324,42 +5324,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385867</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5367,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461920</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700812</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5405,17 +5400,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5434,10 +5425,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385684</v>
+        <v>129385867</v>
       </c>
       <c r="B45" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,26 +5436,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5472,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461868</v>
+        <v>461920</v>
       </c>
       <c r="R45" t="n">
-        <v>6700949</v>
+        <v>6700812</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5510,13 +5506,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B46" t="n">
-        <v>92261</v>
+        <v>91543</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R46" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91507</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>91507</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4466,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>129386306</v>
       </c>
       <c r="B43" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5324,37 +5324,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129385867</v>
       </c>
       <c r="B44" t="n">
-        <v>92261</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5362,10 +5367,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461920</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700812</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5400,13 +5405,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5425,42 +5434,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385867</v>
+        <v>129386264</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>92263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5468,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461920</v>
+        <v>461718</v>
       </c>
       <c r="R45" t="n">
-        <v>6700812</v>
+        <v>6701058</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5506,17 +5510,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385684</v>
+        <v>129385788</v>
       </c>
       <c r="B46" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461868</v>
+        <v>461925</v>
       </c>
       <c r="R46" t="n">
-        <v>6700949</v>
+        <v>6700914</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385788</v>
+        <v>129385753</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461925</v>
+        <v>461960</v>
       </c>
       <c r="R47" t="n">
-        <v>6700914</v>
+        <v>6700969</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385753</v>
+        <v>129385684</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461960</v>
+        <v>461868</v>
       </c>
       <c r="R48" t="n">
-        <v>6700969</v>
+        <v>6700949</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129385673</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385729</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386306</v>
+        <v>129385867</v>
       </c>
       <c r="B43" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,22 +5238,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5261,10 +5270,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461691</v>
+        <v>461920</v>
       </c>
       <c r="R43" t="n">
-        <v>6700983</v>
+        <v>6700812</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5299,13 +5308,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5324,10 +5337,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385867</v>
+        <v>129385684</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5335,31 +5348,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5367,10 +5375,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461920</v>
+        <v>461868</v>
       </c>
       <c r="R44" t="n">
-        <v>6700812</v>
+        <v>6700949</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5405,17 +5413,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5434,32 +5438,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386264</v>
+        <v>129385788</v>
       </c>
       <c r="B45" t="n">
-        <v>92263</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5472,10 +5476,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461718</v>
+        <v>461925</v>
       </c>
       <c r="R45" t="n">
-        <v>6701058</v>
+        <v>6700914</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5535,7 +5539,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385788</v>
+        <v>129385753</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5573,10 +5577,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461925</v>
+        <v>461960</v>
       </c>
       <c r="R46" t="n">
-        <v>6700914</v>
+        <v>6700969</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,10 +5640,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,23 +5651,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R47" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B48" t="n">
-        <v>91545</v>
+        <v>92267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R48" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,26 +6895,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6927,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R59" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6960,13 +6965,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,31 +7005,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R60" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,17 +7070,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7297,42 +7297,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129385644</v>
+        <v>129386570</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7340,10 +7344,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461812</v>
+        <v>461630</v>
       </c>
       <c r="R63" t="n">
-        <v>6700990</v>
+        <v>6700920</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7378,17 +7382,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385937</v>
+        <v>129385644</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461812</v>
       </c>
       <c r="R64" t="n">
-        <v>6700825</v>
+        <v>6700990</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,46 +7517,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129386570</v>
+        <v>129385937</v>
       </c>
       <c r="B65" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7564,10 +7560,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461630</v>
+        <v>461930</v>
       </c>
       <c r="R65" t="n">
-        <v>6700920</v>
+        <v>6700825</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7602,13 +7598,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4466,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91513</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385867</v>
+        <v>129385684</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,31 +5238,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5270,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461920</v>
+        <v>461868</v>
       </c>
       <c r="R43" t="n">
-        <v>6700812</v>
+        <v>6700949</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5308,17 +5303,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5337,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>91549</v>
+        <v>92268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5375,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5438,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5449,26 +5440,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5476,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R45" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5514,13 +5510,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5539,10 +5539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5550,23 +5550,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5577,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R46" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5640,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129386306</v>
+        <v>129385788</v>
       </c>
       <c r="B47" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5651,19 +5647,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461691</v>
+        <v>461925</v>
       </c>
       <c r="R47" t="n">
-        <v>6700983</v>
+        <v>6700914</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386264</v>
+        <v>129385753</v>
       </c>
       <c r="B48" t="n">
-        <v>92267</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461718</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6701058</v>
+        <v>6700969</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>91513</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>91549</v>
+        <v>91514</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R58" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,31 +6895,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6927,10 +6922,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R59" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6965,17 +6960,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7005,26 +6996,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7032,10 +7028,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R60" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7070,13 +7066,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>129386570</v>
       </c>
       <c r="B63" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -5328,34 +5328,30 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129386306</v>
       </c>
       <c r="B44" t="n">
-        <v>92268</v>
+        <v>91570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461691</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700983</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5539,30 +5535,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386306</v>
+        <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>91570</v>
+        <v>92268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461691</v>
+        <v>461718</v>
       </c>
       <c r="R46" t="n">
-        <v>6700983</v>
+        <v>6701058</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7297,46 +7297,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129386570</v>
+        <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7344,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461630</v>
+        <v>461812</v>
       </c>
       <c r="R63" t="n">
-        <v>6700920</v>
+        <v>6700990</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7382,13 +7378,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385644</v>
+        <v>129385937</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461812</v>
+        <v>461930</v>
       </c>
       <c r="R64" t="n">
-        <v>6700990</v>
+        <v>6700825</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,42 +7517,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385937</v>
+        <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7560,10 +7564,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461930</v>
+        <v>461630</v>
       </c>
       <c r="R65" t="n">
-        <v>6700825</v>
+        <v>6700920</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7598,17 +7602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4796,37 +4796,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B39" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4872,13 +4877,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,42 +4906,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385966</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4953,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461831</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700895</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4991,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,46 +5016,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129385719</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461960</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700956</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5227,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B43" t="n">
-        <v>91550</v>
+        <v>92268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R43" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5535,32 +5535,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B46" t="n">
-        <v>92268</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R46" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>91514</v>
+        <v>91550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R58" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4368,7 +4368,7 @@
         <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4796,42 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,17 +4872,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4906,46 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4953,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4991,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5016,37 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>91514</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5227,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B43" t="n">
-        <v>92268</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R43" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B44" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,19 +5339,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R44" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5425,42 +5429,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385867</v>
+        <v>129386264</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5468,10 +5467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461920</v>
+        <v>461718</v>
       </c>
       <c r="R45" t="n">
-        <v>6700812</v>
+        <v>6701058</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5506,17 +5505,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5530,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385684</v>
+        <v>129386306</v>
       </c>
       <c r="B46" t="n">
-        <v>91550</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5546,23 +5541,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5573,10 +5564,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461868</v>
+        <v>461691</v>
       </c>
       <c r="R46" t="n">
-        <v>6700949</v>
+        <v>6700983</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,10 +5627,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,26 +5638,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5670,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R47" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,13 +5708,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385753</v>
+        <v>129385788</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461960</v>
+        <v>461925</v>
       </c>
       <c r="R48" t="n">
-        <v>6700969</v>
+        <v>6700914</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91550</v>
+        <v>91517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>91514</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,26 +6895,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6927,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R59" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6960,13 +6965,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,31 +7005,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R60" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,17 +7070,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385673</v>
+        <v>129385729</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461869</v>
+        <v>461948</v>
       </c>
       <c r="R61" t="n">
         <v>6700980</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129385729</v>
+        <v>129385673</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461948</v>
+        <v>461869</v>
       </c>
       <c r="R62" t="n">
         <v>6700980</v>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,37 +4796,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4843,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4897,42 +4906,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4982,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,46 +5007,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5050,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5092,13 +5088,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385684</v>
+        <v>129385867</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,26 +5238,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5265,10 +5270,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461868</v>
+        <v>461920</v>
       </c>
       <c r="R43" t="n">
-        <v>6700949</v>
+        <v>6700812</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5303,13 +5308,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5328,10 +5337,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,23 +5348,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5366,10 +5371,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R44" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5429,32 +5434,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B45" t="n">
-        <v>92271</v>
+        <v>91553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5467,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R45" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5530,30 +5535,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386306</v>
+        <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>92271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5564,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461691</v>
+        <v>461718</v>
       </c>
       <c r="R46" t="n">
-        <v>6700983</v>
+        <v>6701058</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5627,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385867</v>
+        <v>129385788</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,31 +5647,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5670,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461920</v>
+        <v>461925</v>
       </c>
       <c r="R47" t="n">
-        <v>6700812</v>
+        <v>6700914</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5708,17 +5712,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385788</v>
+        <v>129385753</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461925</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6700914</v>
+        <v>6700969</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,31 +6895,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6927,10 +6922,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R59" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6965,17 +6960,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7005,26 +6996,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7032,10 +7028,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R60" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7070,13 +7066,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385729</v>
+        <v>129385673</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461948</v>
+        <v>461869</v>
       </c>
       <c r="R61" t="n">
         <v>6700980</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129385673</v>
+        <v>129385729</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461869</v>
+        <v>461948</v>
       </c>
       <c r="R62" t="n">
         <v>6700980</v>
@@ -7297,42 +7297,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129385644</v>
+        <v>129386570</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7340,10 +7344,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461812</v>
+        <v>461630</v>
       </c>
       <c r="R63" t="n">
-        <v>6700990</v>
+        <v>6700920</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7378,17 +7382,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385937</v>
+        <v>129385644</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461812</v>
       </c>
       <c r="R64" t="n">
-        <v>6700825</v>
+        <v>6700990</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,46 +7517,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129386570</v>
+        <v>129385937</v>
       </c>
       <c r="B65" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7564,10 +7560,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461630</v>
+        <v>461930</v>
       </c>
       <c r="R65" t="n">
-        <v>6700920</v>
+        <v>6700825</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7602,13 +7598,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4796,46 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385966</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4843,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461831</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700895</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4906,37 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4982,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,42 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129386074</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5050,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461874</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700850</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5088,17 +5092,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5337,30 +5337,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386306</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>91573</v>
+        <v>92271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5371,10 +5375,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461691</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700983</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5535,34 +5539,30 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386264</v>
+        <v>129386306</v>
       </c>
       <c r="B46" t="n">
-        <v>92271</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461718</v>
+        <v>461691</v>
       </c>
       <c r="R46" t="n">
-        <v>6701058</v>
+        <v>6700983</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4466,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,37 +4796,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4843,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5007,46 +5016,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129385719</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461960</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700956</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5227,42 +5227,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385867</v>
+        <v>129386264</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5270,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461920</v>
+        <v>461718</v>
       </c>
       <c r="R43" t="n">
-        <v>6700812</v>
+        <v>6701058</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5308,17 +5303,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5337,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129385788</v>
       </c>
       <c r="B44" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5375,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461925</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700914</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5438,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385684</v>
+        <v>129385753</v>
       </c>
       <c r="B45" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5449,21 +5440,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5476,10 +5467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461868</v>
+        <v>461960</v>
       </c>
       <c r="R45" t="n">
-        <v>6700949</v>
+        <v>6700969</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5539,10 +5530,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386306</v>
+        <v>129385684</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5550,19 +5541,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461691</v>
+        <v>461868</v>
       </c>
       <c r="R46" t="n">
-        <v>6700983</v>
+        <v>6700949</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5636,10 +5631,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,26 +5642,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R47" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,13 +5712,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,10 +5741,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5748,23 +5752,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R48" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R58" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7297,46 +7297,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129386570</v>
+        <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7344,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461630</v>
+        <v>461812</v>
       </c>
       <c r="R63" t="n">
-        <v>6700920</v>
+        <v>6700990</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7382,13 +7378,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385644</v>
+        <v>129385937</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461812</v>
+        <v>461930</v>
       </c>
       <c r="R64" t="n">
-        <v>6700990</v>
+        <v>6700825</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,42 +7517,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385937</v>
+        <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7560,10 +7564,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461930</v>
+        <v>461630</v>
       </c>
       <c r="R65" t="n">
-        <v>6700825</v>
+        <v>6700920</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7598,17 +7602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,46 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385966</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4843,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461831</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700895</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5016,37 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5227,37 +5227,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386264</v>
+        <v>129385867</v>
       </c>
       <c r="B43" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5265,10 +5270,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461718</v>
+        <v>461920</v>
       </c>
       <c r="R43" t="n">
-        <v>6701058</v>
+        <v>6700812</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5303,13 +5308,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5328,10 +5337,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385788</v>
+        <v>129386306</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,23 +5348,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5366,10 +5371,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461925</v>
+        <v>461691</v>
       </c>
       <c r="R44" t="n">
-        <v>6700914</v>
+        <v>6700983</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5429,10 +5434,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385753</v>
+        <v>129385684</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5440,21 +5445,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5467,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461960</v>
+        <v>461868</v>
       </c>
       <c r="R45" t="n">
-        <v>6700969</v>
+        <v>6700949</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5530,32 +5535,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>92271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R46" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5631,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385867</v>
+        <v>129385788</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5642,31 +5647,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461920</v>
+        <v>461925</v>
       </c>
       <c r="R47" t="n">
-        <v>6700812</v>
+        <v>6700914</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,17 +5712,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5741,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B48" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,19 +5748,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,26 +6895,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6927,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R59" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6960,13 +6965,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,31 +7005,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R60" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,17 +7070,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4466,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,37 +4796,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4872,13 +4877,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,42 +4906,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4982,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385867</v>
+        <v>129385788</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,31 +5238,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5270,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461920</v>
+        <v>461925</v>
       </c>
       <c r="R43" t="n">
-        <v>6700812</v>
+        <v>6700914</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5308,17 +5303,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5337,10 +5328,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B44" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5348,19 +5339,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R44" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5434,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385684</v>
+        <v>129386306</v>
       </c>
       <c r="B45" t="n">
-        <v>91553</v>
+        <v>91573</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,23 +5440,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -5472,10 +5463,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461868</v>
+        <v>461691</v>
       </c>
       <c r="R45" t="n">
-        <v>6700949</v>
+        <v>6700983</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5535,37 +5526,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386264</v>
+        <v>129385867</v>
       </c>
       <c r="B46" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5573,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461718</v>
+        <v>461920</v>
       </c>
       <c r="R46" t="n">
-        <v>6701058</v>
+        <v>6700812</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5611,13 +5607,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385788</v>
+        <v>129385684</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,21 +5647,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461925</v>
+        <v>461868</v>
       </c>
       <c r="R47" t="n">
-        <v>6700914</v>
+        <v>6700949</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385753</v>
+        <v>129386264</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461960</v>
+        <v>461718</v>
       </c>
       <c r="R48" t="n">
-        <v>6700969</v>
+        <v>6701058</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,31 +6895,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6927,10 +6922,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R59" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6965,17 +6960,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7005,26 +6996,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7032,10 +7028,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R60" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7070,13 +7066,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385673</v>
+        <v>129385729</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461869</v>
+        <v>461948</v>
       </c>
       <c r="R61" t="n">
         <v>6700980</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129385729</v>
+        <v>129385673</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461948</v>
+        <v>461869</v>
       </c>
       <c r="R62" t="n">
         <v>6700980</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4368,7 +4368,7 @@
         <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>129386134</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>129386082</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4796,42 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,17 +4872,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4906,37 +4897,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385719</v>
+        <v>129385966</v>
       </c>
       <c r="B40" t="n">
-        <v>91517</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461960</v>
+        <v>461831</v>
       </c>
       <c r="R40" t="n">
-        <v>6700956</v>
+        <v>6700895</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5007,46 +5007,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5050,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5092,13 +5088,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>129386552</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385788</v>
+        <v>129385684</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,21 +5238,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461925</v>
+        <v>461868</v>
       </c>
       <c r="R43" t="n">
-        <v>6700914</v>
+        <v>6700949</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385753</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>92299</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461960</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700969</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B45" t="n">
-        <v>91573</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5440,19 +5440,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R45" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5526,10 +5530,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385867</v>
+        <v>129386306</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,31 +5541,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461920</v>
+        <v>461691</v>
       </c>
       <c r="R46" t="n">
-        <v>6700812</v>
+        <v>6700983</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5607,17 +5602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5627,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385684</v>
+        <v>129385867</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,26 +5638,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5670,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461868</v>
+        <v>461920</v>
       </c>
       <c r="R47" t="n">
-        <v>6700949</v>
+        <v>6700812</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,13 +5708,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386264</v>
+        <v>129385788</v>
       </c>
       <c r="B48" t="n">
-        <v>92271</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461718</v>
+        <v>461925</v>
       </c>
       <c r="R48" t="n">
-        <v>6701058</v>
+        <v>6700914</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>129386716</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>129386225</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>129386256</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>91517</v>
+        <v>91581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R58" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6887,7 +6887,7 @@
         <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129385729</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385673</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>129385937</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57730</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>91545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5227,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B43" t="n">
-        <v>91581</v>
+        <v>92299</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R43" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129385788</v>
       </c>
       <c r="B44" t="n">
-        <v>92299</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461925</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700914</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385788</v>
+        <v>129385684</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>91581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461925</v>
+        <v>461868</v>
       </c>
       <c r="R48" t="n">
-        <v>6700914</v>
+        <v>6700949</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385729</v>
+        <v>129385673</v>
       </c>
       <c r="B61" t="n">
         <v>79070</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461948</v>
+        <v>461869</v>
       </c>
       <c r="R61" t="n">
         <v>6700980</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129385673</v>
+        <v>129385729</v>
       </c>
       <c r="B62" t="n">
         <v>79070</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461869</v>
+        <v>461948</v>
       </c>
       <c r="R62" t="n">
         <v>6700980</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,42 +4365,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>91551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461809</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,17 +4441,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4475,10 +4466,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>129386134</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4518,10 +4509,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461791</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700853</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,7 +4549,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4576,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>91545</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,10 +4619,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461823</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6700883</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4661,13 +4657,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>129386082</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4897,46 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4982,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,42 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129386074</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5050,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461874</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700850</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5088,17 +5092,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>129386552</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,34 +5227,30 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386264</v>
+        <v>129386306</v>
       </c>
       <c r="B43" t="n">
-        <v>92299</v>
+        <v>91607</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -5265,10 +5261,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461718</v>
+        <v>461691</v>
       </c>
       <c r="R43" t="n">
-        <v>6701058</v>
+        <v>6700983</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5331,7 +5327,7 @@
         <v>129385788</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5432,7 +5428,7 @@
         <v>129385753</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5530,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386306</v>
+        <v>129385867</v>
       </c>
       <c r="B46" t="n">
-        <v>91601</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5541,22 +5537,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461691</v>
+        <v>461920</v>
       </c>
       <c r="R46" t="n">
-        <v>6700983</v>
+        <v>6700812</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5602,13 +5607,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5627,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385867</v>
+        <v>129385684</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,31 +5647,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5670,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461920</v>
+        <v>461868</v>
       </c>
       <c r="R47" t="n">
-        <v>6700812</v>
+        <v>6700949</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5708,17 +5712,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B48" t="n">
-        <v>91581</v>
+        <v>92305</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R48" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>129386716</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>129386225</v>
       </c>
       <c r="B51" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>129386256</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>91587</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>91581</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6786,7 +6786,7 @@
         <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129385673</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385729</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>129385937</v>
       </c>
       <c r="B64" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4368,7 +4368,7 @@
         <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>129386134</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129386049</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>129386082</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4796,37 +4796,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4872,13 +4877,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,42 +4906,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>91552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4982,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>129386552</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>129386306</v>
       </c>
       <c r="B43" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>129385788</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>129385753</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5526,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385867</v>
+        <v>129385684</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,31 +5537,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461920</v>
+        <v>461868</v>
       </c>
       <c r="R46" t="n">
-        <v>6700812</v>
+        <v>6700949</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5607,17 +5602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5636,32 +5627,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B47" t="n">
-        <v>91587</v>
+        <v>92306</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5665,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R47" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,37 +5728,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386264</v>
+        <v>129385867</v>
       </c>
       <c r="B48" t="n">
-        <v>92305</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5775,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461718</v>
+        <v>461920</v>
       </c>
       <c r="R48" t="n">
-        <v>6701058</v>
+        <v>6700812</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5813,13 +5809,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>129386716</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>129386225</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>129386256</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B56" t="n">
-        <v>91587</v>
+        <v>91552</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6685,7 +6685,7 @@
         <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>91551</v>
+        <v>91588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,26 +6895,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6927,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R59" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6960,13 +6965,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,31 +7005,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R60" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,17 +7070,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>129385673</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385729</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7297,42 +7297,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129385644</v>
+        <v>129386570</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7340,10 +7344,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461812</v>
+        <v>461630</v>
       </c>
       <c r="R63" t="n">
-        <v>6700990</v>
+        <v>6700920</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7378,17 +7382,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385937</v>
+        <v>129385644</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461812</v>
       </c>
       <c r="R64" t="n">
-        <v>6700825</v>
+        <v>6700990</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,46 +7517,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129386570</v>
+        <v>129385937</v>
       </c>
       <c r="B65" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7564,10 +7560,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461630</v>
+        <v>461930</v>
       </c>
       <c r="R65" t="n">
-        <v>6700920</v>
+        <v>6700825</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7602,13 +7598,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4796,42 +4796,46 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385966</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4839,10 +4843,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461831</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700895</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,17 +4881,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5007,46 +5007,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129386074</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +5050,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461874</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700850</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5092,13 +5088,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386187</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91552</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461816</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6700916</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>91588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>91588</v>
+        <v>91552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R58" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4368,7 +4368,7 @@
         <v>129386181</v>
       </c>
       <c r="B35" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4796,46 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385966</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>91557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4843,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461831</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700895</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4906,37 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>91552</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4982,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,42 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129386074</v>
+        <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5050,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461874</v>
+        <v>461831</v>
       </c>
       <c r="R41" t="n">
-        <v>6700850</v>
+        <v>6700895</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5088,17 +5092,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386306</v>
+        <v>129385684</v>
       </c>
       <c r="B43" t="n">
-        <v>91608</v>
+        <v>91593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,19 +5238,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -5261,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461691</v>
+        <v>461868</v>
       </c>
       <c r="R43" t="n">
-        <v>6700983</v>
+        <v>6700949</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5324,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385788</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>92311</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461925</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700914</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5425,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,23 +5440,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R45" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5526,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385684</v>
+        <v>129385788</v>
       </c>
       <c r="B46" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,21 +5537,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461868</v>
+        <v>461925</v>
       </c>
       <c r="R46" t="n">
-        <v>6700949</v>
+        <v>6700914</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129386264</v>
+        <v>129385753</v>
       </c>
       <c r="B47" t="n">
-        <v>92306</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461718</v>
+        <v>461960</v>
       </c>
       <c r="R47" t="n">
-        <v>6701058</v>
+        <v>6700969</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129385780</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129385669</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129386288</v>
       </c>
       <c r="B55" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,31 +6895,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6927,10 +6922,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R59" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6965,17 +6960,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7005,26 +6996,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7032,10 +7028,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R60" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7070,13 +7066,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>129385673</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129385729</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7297,46 +7297,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129386570</v>
+        <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7344,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461630</v>
+        <v>461812</v>
       </c>
       <c r="R63" t="n">
-        <v>6700920</v>
+        <v>6700990</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7382,13 +7378,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385644</v>
+        <v>129385937</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461812</v>
+        <v>461930</v>
       </c>
       <c r="R64" t="n">
-        <v>6700990</v>
+        <v>6700825</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,42 +7517,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385937</v>
+        <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7560,10 +7564,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461930</v>
+        <v>461630</v>
       </c>
       <c r="R65" t="n">
-        <v>6700825</v>
+        <v>6700920</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7598,17 +7602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4796,37 +4796,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B39" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4872,13 +4877,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,42 +4906,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4982,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385684</v>
+        <v>129385788</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,21 +5238,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461868</v>
+        <v>461925</v>
       </c>
       <c r="R43" t="n">
-        <v>6700949</v>
+        <v>6700914</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,32 +5328,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129385753</v>
       </c>
       <c r="B44" t="n">
-        <v>92311</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461960</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700969</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386306</v>
+        <v>129385684</v>
       </c>
       <c r="B45" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5440,19 +5440,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461691</v>
+        <v>461868</v>
       </c>
       <c r="R45" t="n">
-        <v>6700983</v>
+        <v>6700949</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5526,32 +5530,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385788</v>
+        <v>129386264</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5564,10 +5568,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461925</v>
+        <v>461718</v>
       </c>
       <c r="R46" t="n">
-        <v>6700914</v>
+        <v>6701058</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5627,10 +5631,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385753</v>
+        <v>129386306</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,23 +5642,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461960</v>
+        <v>461691</v>
       </c>
       <c r="R47" t="n">
-        <v>6700969</v>
+        <v>6700983</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B57" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4796,42 +4796,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,17 +4872,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4906,37 +4897,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B40" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4940,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R40" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4982,13 +4978,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385788</v>
+        <v>129386306</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,23 +5238,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -5265,10 +5261,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461925</v>
+        <v>461691</v>
       </c>
       <c r="R43" t="n">
-        <v>6700914</v>
+        <v>6700983</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5328,32 +5324,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129385753</v>
+        <v>129386264</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461960</v>
+        <v>461718</v>
       </c>
       <c r="R44" t="n">
-        <v>6700969</v>
+        <v>6701058</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5530,32 +5526,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129386264</v>
+        <v>129385788</v>
       </c>
       <c r="B46" t="n">
-        <v>92311</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5568,10 +5564,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461718</v>
+        <v>461925</v>
       </c>
       <c r="R46" t="n">
-        <v>6701058</v>
+        <v>6700914</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5631,10 +5627,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129386306</v>
+        <v>129385753</v>
       </c>
       <c r="B47" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5642,19 +5638,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461691</v>
+        <v>461960</v>
       </c>
       <c r="R47" t="n">
-        <v>6700983</v>
+        <v>6700969</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129386187</v>
       </c>
       <c r="B56" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461816</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B58" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129386306</v>
+        <v>129385788</v>
       </c>
       <c r="B43" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,19 +5238,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -5261,10 +5265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461691</v>
+        <v>461925</v>
       </c>
       <c r="R43" t="n">
-        <v>6700983</v>
+        <v>6700914</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5324,34 +5328,30 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386264</v>
+        <v>129386306</v>
       </c>
       <c r="B44" t="n">
-        <v>92311</v>
+        <v>91613</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461718</v>
+        <v>461691</v>
       </c>
       <c r="R44" t="n">
-        <v>6701058</v>
+        <v>6700983</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385684</v>
+        <v>129385753</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,21 +5436,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461868</v>
+        <v>461960</v>
       </c>
       <c r="R45" t="n">
-        <v>6700949</v>
+        <v>6700969</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5526,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,26 +5537,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R46" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5602,13 +5607,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5627,32 +5636,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385753</v>
+        <v>129386264</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5665,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461960</v>
+        <v>461718</v>
       </c>
       <c r="R47" t="n">
-        <v>6700969</v>
+        <v>6701058</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5728,10 +5737,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385867</v>
+        <v>129385684</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5739,31 +5748,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5771,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461920</v>
+        <v>461868</v>
       </c>
       <c r="R48" t="n">
-        <v>6700812</v>
+        <v>6700949</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5809,17 +5813,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6370,37 +6370,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129385669</v>
+        <v>129386288</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6408,10 +6417,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461858</v>
+        <v>461678</v>
       </c>
       <c r="R54" t="n">
-        <v>6700997</v>
+        <v>6700995</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6471,46 +6480,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129386288</v>
+        <v>129385669</v>
       </c>
       <c r="B55" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461678</v>
+        <v>461858</v>
       </c>
       <c r="R55" t="n">
-        <v>6700995</v>
+        <v>6700997</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6581,32 +6581,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B56" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R56" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,21 +6794,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129385764</v>
+        <v>129386062</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,26 +6895,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6927,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461972</v>
+        <v>461861</v>
       </c>
       <c r="R59" t="n">
-        <v>6700967</v>
+        <v>6700879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6960,13 +6965,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6985,10 +6994,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129386062</v>
+        <v>129385764</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6996,31 +7005,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461861</v>
+        <v>461972</v>
       </c>
       <c r="R60" t="n">
-        <v>6700879</v>
+        <v>6700967</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7066,17 +7070,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7297,42 +7297,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129385644</v>
+        <v>129386570</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7340,10 +7344,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461812</v>
+        <v>461630</v>
       </c>
       <c r="R63" t="n">
-        <v>6700990</v>
+        <v>6700920</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7378,17 +7382,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385937</v>
+        <v>129385644</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461812</v>
       </c>
       <c r="R64" t="n">
-        <v>6700825</v>
+        <v>6700990</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,46 +7517,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129386570</v>
+        <v>129385937</v>
       </c>
       <c r="B65" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7564,10 +7560,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461630</v>
+        <v>461930</v>
       </c>
       <c r="R65" t="n">
-        <v>6700920</v>
+        <v>6700825</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7602,13 +7598,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4365,37 +4365,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386181</v>
+        <v>129386134</v>
       </c>
       <c r="B35" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461809</v>
+        <v>461791</v>
       </c>
       <c r="R35" t="n">
-        <v>6700924</v>
+        <v>6700853</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4441,13 +4446,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4475,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386134</v>
+        <v>129386049</v>
       </c>
       <c r="B36" t="n">
         <v>57736</v>
@@ -4509,10 +4518,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461791</v>
+        <v>461823</v>
       </c>
       <c r="R36" t="n">
-        <v>6700853</v>
+        <v>6700883</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall, rikligt med kåda.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,42 +4585,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386049</v>
+        <v>129386181</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4619,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461823</v>
+        <v>461809</v>
       </c>
       <c r="R37" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4657,17 +4661,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4796,37 +4796,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129385719</v>
+        <v>129386074</v>
       </c>
       <c r="B39" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4834,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461960</v>
+        <v>461874</v>
       </c>
       <c r="R39" t="n">
-        <v>6700956</v>
+        <v>6700850</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4872,13 +4877,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4897,42 +4906,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129386074</v>
+        <v>129385719</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4940,10 +4944,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461874</v>
+        <v>461960</v>
       </c>
       <c r="R40" t="n">
-        <v>6700850</v>
+        <v>6700956</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4978,17 +4982,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>129385966</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385788</v>
+        <v>129385867</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,26 +5238,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5265,10 +5270,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461925</v>
+        <v>461920</v>
       </c>
       <c r="R43" t="n">
-        <v>6700914</v>
+        <v>6700812</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5303,13 +5308,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5331,7 +5340,7 @@
         <v>129386306</v>
       </c>
       <c r="B44" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5425,7 +5434,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385753</v>
+        <v>129385788</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5463,10 +5472,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461960</v>
+        <v>461925</v>
       </c>
       <c r="R45" t="n">
-        <v>6700969</v>
+        <v>6700914</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5526,10 +5535,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385867</v>
+        <v>129385753</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,31 +5546,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5569,10 +5573,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461920</v>
+        <v>461960</v>
       </c>
       <c r="R46" t="n">
-        <v>6700812</v>
+        <v>6700969</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5607,17 +5611,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5636,32 +5636,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129386264</v>
+        <v>129385684</v>
       </c>
       <c r="B47" t="n">
-        <v>92311</v>
+        <v>91597</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461718</v>
+        <v>461868</v>
       </c>
       <c r="R47" t="n">
-        <v>6701058</v>
+        <v>6700949</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129385684</v>
+        <v>129386264</v>
       </c>
       <c r="B48" t="n">
-        <v>91593</v>
+        <v>92315</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461868</v>
+        <v>461718</v>
       </c>
       <c r="R48" t="n">
-        <v>6700949</v>
+        <v>6701058</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,7 +5841,7 @@
         <v>129386233</v>
       </c>
       <c r="B49" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129386288</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129386272</v>
+        <v>129385794</v>
       </c>
       <c r="B56" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6592,21 +6592,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461685</v>
+        <v>461932</v>
       </c>
       <c r="R56" t="n">
-        <v>6701059</v>
+        <v>6700907</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6682,32 +6682,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386187</v>
+        <v>129386272</v>
       </c>
       <c r="B57" t="n">
-        <v>91557</v>
+        <v>91597</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461816</v>
+        <v>461685</v>
       </c>
       <c r="R57" t="n">
-        <v>6700916</v>
+        <v>6701059</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6783,32 +6783,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129385794</v>
+        <v>129386187</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91561</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461932</v>
+        <v>461816</v>
       </c>
       <c r="R58" t="n">
-        <v>6700907</v>
+        <v>6700916</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7297,46 +7297,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129386570</v>
+        <v>129385644</v>
       </c>
       <c r="B63" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7344,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461630</v>
+        <v>461812</v>
       </c>
       <c r="R63" t="n">
-        <v>6700920</v>
+        <v>6700990</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7382,13 +7378,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385644</v>
+        <v>129385937</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -7450,10 +7450,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461812</v>
+        <v>461930</v>
       </c>
       <c r="R64" t="n">
-        <v>6700990</v>
+        <v>6700825</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7517,42 +7517,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385937</v>
+        <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7560,10 +7564,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461930</v>
+        <v>461630</v>
       </c>
       <c r="R65" t="n">
-        <v>6700825</v>
+        <v>6700920</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7598,17 +7602,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>129386729</v>
       </c>
       <c r="B66" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124175534</v>
+        <v>124174869</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461735</v>
+        <v>461848</v>
       </c>
       <c r="R2" t="n">
-        <v>6701055</v>
+        <v>6700855</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,51 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124176275</v>
+        <v>124174890</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461688</v>
+        <v>461855</v>
       </c>
       <c r="R3" t="n">
-        <v>6700885</v>
+        <v>6700846</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -905,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124175914</v>
+        <v>124176071</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,39 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461694</v>
+        <v>461708</v>
       </c>
       <c r="R4" t="n">
-        <v>6700999</v>
+        <v>6700899</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,51 +978,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124175453</v>
+        <v>129385684</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461792</v>
+        <v>461868</v>
       </c>
       <c r="R5" t="n">
-        <v>6700952</v>
+        <v>6700949</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124175266</v>
+        <v>129386233</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,13 +1117,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461917</v>
+        <v>461767</v>
       </c>
       <c r="R6" t="n">
-        <v>6700885</v>
+        <v>6700964</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124175498</v>
+        <v>129386272</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,31 +1191,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461876</v>
+        <v>461685</v>
       </c>
       <c r="R7" t="n">
-        <v>6700933</v>
+        <v>6701059</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,17 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1262,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,51 +1281,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124175111</v>
+        <v>129386326</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461897</v>
+        <v>461677</v>
       </c>
       <c r="R8" t="n">
-        <v>6700803</v>
+        <v>6700973</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124175718</v>
+        <v>124174932</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,28 +1393,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1521,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461713</v>
+        <v>461851</v>
       </c>
       <c r="R9" t="n">
-        <v>6701043</v>
+        <v>6700848</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1563,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1584,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124175647</v>
+        <v>129386264</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,35 +1494,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1636,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461689</v>
+        <v>461718</v>
       </c>
       <c r="R10" t="n">
-        <v>6701105</v>
+        <v>6701058</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,12 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,6 +1565,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1698,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124174911</v>
+        <v>129386382</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,25 +1595,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1741,13 +1630,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461858</v>
+        <v>461672</v>
       </c>
       <c r="R11" t="n">
-        <v>6700851</v>
+        <v>6700932</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,12 +1660,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,44 +1693,35 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124175776</v>
+        <v>129385719</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1851,13 +1731,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461720</v>
+        <v>461960</v>
       </c>
       <c r="R12" t="n">
-        <v>6701011</v>
+        <v>6700956</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,37 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124175215</v>
+        <v>129386181</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,13 +1832,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461931</v>
+        <v>461809</v>
       </c>
       <c r="R13" t="n">
-        <v>6700883</v>
+        <v>6700924</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,12 +1862,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,15 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124176373</v>
+        <v>129386187</v>
       </c>
       <c r="B14" t="n">
-        <v>92326</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,28 +1906,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2067,13 +1933,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461655</v>
+        <v>461816</v>
       </c>
       <c r="R14" t="n">
-        <v>6700853</v>
+        <v>6700916</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,12 +1963,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124174869</v>
+        <v>124176373</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,24 +2007,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2173,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461848</v>
+        <v>461655</v>
       </c>
       <c r="R15" t="n">
-        <v>6700855</v>
+        <v>6700853</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2236,15 +2101,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124174681</v>
+        <v>129386729</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,39 +2112,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2292,13 +2147,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461777</v>
+        <v>461658</v>
       </c>
       <c r="R16" t="n">
-        <v>6700942</v>
+        <v>6700848</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,12 +2177,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,6 +2191,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2354,15 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124176290</v>
+        <v>124174911</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,35 +2221,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2406,10 +2248,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461688</v>
+        <v>461858</v>
       </c>
       <c r="R17" t="n">
-        <v>6700877</v>
+        <v>6700851</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2469,55 +2311,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124175959</v>
+        <v>124175215</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2525,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461702</v>
+        <v>461931</v>
       </c>
       <c r="R18" t="n">
-        <v>6701001</v>
+        <v>6700883</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2569,6 +2393,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2587,15 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124175156</v>
+        <v>124175266</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,35 +2423,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2639,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461943</v>
+        <v>461917</v>
       </c>
       <c r="R19" t="n">
-        <v>6700846</v>
+        <v>6700885</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2702,47 +2513,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124175587</v>
+        <v>124175346</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2750,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461706</v>
+        <v>461868</v>
       </c>
       <c r="R20" t="n">
-        <v>6701095</v>
+        <v>6700927</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2780,17 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,6 +2595,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2817,55 +2614,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124174819</v>
+        <v>124175381</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2873,10 +2652,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461833</v>
+        <v>461839</v>
       </c>
       <c r="R21" t="n">
-        <v>6700849</v>
+        <v>6700986</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2917,6 +2696,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2935,19 +2715,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124175346</v>
+        <v>124175739</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2978,10 +2753,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461868</v>
+        <v>461713</v>
       </c>
       <c r="R22" t="n">
-        <v>6700927</v>
+        <v>6701035</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3041,19 +2816,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124175739</v>
+        <v>124176021</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3084,10 +2854,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461713</v>
+        <v>461747</v>
       </c>
       <c r="R23" t="n">
-        <v>6701035</v>
+        <v>6700906</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3147,37 +2917,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124176071</v>
+        <v>129385654</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,13 +2955,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461708</v>
+        <v>461827</v>
       </c>
       <c r="R24" t="n">
-        <v>6700899</v>
+        <v>6700993</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3220,12 +2985,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3253,15 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124174932</v>
+        <v>129385669</v>
       </c>
       <c r="B25" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,21 +3029,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,13 +3056,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461851</v>
+        <v>461858</v>
       </c>
       <c r="R25" t="n">
-        <v>6700848</v>
+        <v>6700997</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,19 +3086,19 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
@@ -3359,19 +3119,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124176021</v>
+        <v>129385673</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3402,13 +3157,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461747</v>
+        <v>461869</v>
       </c>
       <c r="R26" t="n">
-        <v>6700906</v>
+        <v>6700980</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3432,12 +3187,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,44 +3220,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124176170</v>
+        <v>129385729</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3512,13 +3258,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461712</v>
+        <v>461948</v>
       </c>
       <c r="R27" t="n">
-        <v>6700887</v>
+        <v>6700980</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3542,12 +3288,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,19 +3321,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124175381</v>
+        <v>129385753</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3618,13 +3359,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461839</v>
+        <v>461960</v>
       </c>
       <c r="R28" t="n">
-        <v>6700986</v>
+        <v>6700969</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3648,12 +3389,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3681,15 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124175075</v>
+        <v>129385764</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,35 +3433,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3733,13 +3460,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461846</v>
+        <v>461972</v>
       </c>
       <c r="R29" t="n">
-        <v>6700848</v>
+        <v>6700967</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3763,12 +3490,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3796,15 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124176306</v>
+        <v>129385780</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3812,35 +3534,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3848,13 +3561,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461677</v>
+        <v>461935</v>
       </c>
       <c r="R30" t="n">
-        <v>6700883</v>
+        <v>6700926</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3878,12 +3591,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,55 +3624,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124174707</v>
+        <v>129385788</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3967,13 +3662,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461884</v>
+        <v>461925</v>
       </c>
       <c r="R31" t="n">
-        <v>6700921</v>
+        <v>6700914</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3997,12 +3692,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,6 +3706,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4029,15 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124175319</v>
+        <v>129385794</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,35 +3736,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4081,13 +3763,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461910</v>
+        <v>461932</v>
       </c>
       <c r="R32" t="n">
-        <v>6700899</v>
+        <v>6700907</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4111,12 +3793,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,15 +3826,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124174890</v>
+        <v>124174681</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,26 +3837,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4187,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461855</v>
+        <v>461777</v>
       </c>
       <c r="R33" t="n">
-        <v>6700846</v>
+        <v>6700942</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4231,7 +3921,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4250,51 +3939,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124175050</v>
+        <v>124174707</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4302,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461862</v>
+        <v>461884</v>
       </c>
       <c r="R34" t="n">
-        <v>6700845</v>
+        <v>6700921</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4346,7 +4034,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4365,10 +4052,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129386134</v>
+        <v>124174819</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,12 +4080,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4408,13 +4103,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461791</v>
+        <v>461833</v>
       </c>
       <c r="R35" t="n">
-        <v>6700853</v>
+        <v>6700849</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4438,17 +4133,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4475,10 +4165,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129386049</v>
+        <v>124175498</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4508,7 +4198,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4518,13 +4208,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461823</v>
+        <v>461876</v>
       </c>
       <c r="R36" t="n">
-        <v>6700883</v>
+        <v>6700933</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4548,17 +4238,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt med kåda.</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4585,37 +4275,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129386181</v>
+        <v>124175587</v>
       </c>
       <c r="B37" t="n">
-        <v>91561</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4623,13 +4318,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461809</v>
+        <v>461706</v>
       </c>
       <c r="R37" t="n">
-        <v>6700924</v>
+        <v>6701095</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4653,12 +4348,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4367,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4686,10 +4385,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129386082</v>
+        <v>129385644</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4719,7 +4418,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4729,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461838</v>
+        <v>461812</v>
       </c>
       <c r="R38" t="n">
-        <v>6700865</v>
+        <v>6700990</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4796,10 +4495,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129386074</v>
+        <v>129385867</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4829,7 +4528,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4839,10 +4538,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461874</v>
+        <v>461920</v>
       </c>
       <c r="R39" t="n">
-        <v>6700850</v>
+        <v>6700812</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4906,37 +4605,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129385719</v>
+        <v>129385937</v>
       </c>
       <c r="B40" t="n">
-        <v>91561</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4944,10 +4648,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461960</v>
+        <v>461930</v>
       </c>
       <c r="R40" t="n">
-        <v>6700956</v>
+        <v>6700825</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4982,13 +4686,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5007,46 +4715,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129385966</v>
+        <v>129386049</v>
       </c>
       <c r="B41" t="n">
-        <v>98778</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5054,10 +4758,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461831</v>
+        <v>461823</v>
       </c>
       <c r="R41" t="n">
-        <v>6700895</v>
+        <v>6700883</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5092,13 +4796,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt med kåda.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5117,10 +4825,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129386552</v>
+        <v>129386062</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5150,7 +4858,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5160,10 +4868,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461718</v>
+        <v>461861</v>
       </c>
       <c r="R42" t="n">
-        <v>6700893</v>
+        <v>6700879</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5200,7 +4908,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål i döende gran, angripen av granticka. 2st 4-5 cm runda bohål, 2,5 meter upp på stammen.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +4935,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385867</v>
+        <v>129386074</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5260,7 +4968,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5270,10 +4978,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461920</v>
+        <v>461874</v>
       </c>
       <c r="R43" t="n">
-        <v>6700812</v>
+        <v>6700850</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5337,10 +5045,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386306</v>
+        <v>129386082</v>
       </c>
       <c r="B44" t="n">
-        <v>91617</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5348,22 +5056,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5371,10 +5088,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461691</v>
+        <v>461838</v>
       </c>
       <c r="R44" t="n">
-        <v>6700983</v>
+        <v>6700865</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5409,13 +5126,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5434,10 +5155,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129385788</v>
+        <v>129386134</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,26 +5166,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5472,10 +5198,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461925</v>
+        <v>461791</v>
       </c>
       <c r="R45" t="n">
-        <v>6700914</v>
+        <v>6700853</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5510,13 +5236,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385753</v>
+        <v>129386225</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5546,26 +5276,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5573,10 +5308,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461960</v>
+        <v>461776</v>
       </c>
       <c r="R46" t="n">
-        <v>6700969</v>
+        <v>6700968</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5611,13 +5346,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5375,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385684</v>
+        <v>129386256</v>
       </c>
       <c r="B47" t="n">
-        <v>91597</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,26 +5386,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5674,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461868</v>
+        <v>461731</v>
       </c>
       <c r="R47" t="n">
-        <v>6700949</v>
+        <v>6701017</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5712,13 +5456,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5737,37 +5485,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129386264</v>
+        <v>129386365</v>
       </c>
       <c r="B48" t="n">
-        <v>92315</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5775,10 +5528,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461718</v>
+        <v>461656</v>
       </c>
       <c r="R48" t="n">
-        <v>6701058</v>
+        <v>6700966</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5813,13 +5566,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5838,10 +5595,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129386233</v>
+        <v>129386552</v>
       </c>
       <c r="B49" t="n">
-        <v>91597</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,26 +5606,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5876,10 +5638,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461767</v>
+        <v>461718</v>
       </c>
       <c r="R49" t="n">
-        <v>6700964</v>
+        <v>6700893</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5914,13 +5676,17 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Bohål i döende gran, angripen av granticka. 2st 4-5 cm runda bohål, 2,5 meter upp på stammen.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5939,10 +5705,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129386716</v>
+        <v>129386584</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5972,7 +5738,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5982,10 +5748,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461581</v>
+        <v>461620</v>
       </c>
       <c r="R50" t="n">
-        <v>6700899</v>
+        <v>6700973</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6049,10 +5815,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129386225</v>
+        <v>129386716</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,10 +5858,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461776</v>
+        <v>461581</v>
       </c>
       <c r="R51" t="n">
-        <v>6700968</v>
+        <v>6700899</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6159,40 +5925,44 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129386256</v>
+        <v>124175647</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6202,13 +5972,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461731</v>
+        <v>461689</v>
       </c>
       <c r="R52" t="n">
-        <v>6701017</v>
+        <v>6701105</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6232,17 +6002,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6269,37 +6034,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129385780</v>
+        <v>124175050</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6307,13 +6081,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461935</v>
+        <v>461862</v>
       </c>
       <c r="R53" t="n">
-        <v>6700926</v>
+        <v>6700845</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6337,12 +6111,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6370,10 +6144,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129386288</v>
+        <v>124175075</v>
       </c>
       <c r="B54" t="n">
-        <v>98778</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6417,13 +6191,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461678</v>
+        <v>461846</v>
       </c>
       <c r="R54" t="n">
-        <v>6700995</v>
+        <v>6700848</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6447,12 +6221,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6480,37 +6254,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129385669</v>
+        <v>124175111</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6518,13 +6301,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461858</v>
+        <v>461897</v>
       </c>
       <c r="R55" t="n">
-        <v>6700997</v>
+        <v>6700803</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6548,12 +6331,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6581,37 +6364,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385794</v>
+        <v>124175156</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6619,13 +6411,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461932</v>
+        <v>461943</v>
       </c>
       <c r="R56" t="n">
-        <v>6700907</v>
+        <v>6700846</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6649,12 +6441,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,37 +6474,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129386272</v>
+        <v>124175319</v>
       </c>
       <c r="B57" t="n">
-        <v>91597</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6720,13 +6521,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461685</v>
+        <v>461910</v>
       </c>
       <c r="R57" t="n">
-        <v>6701059</v>
+        <v>6700899</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6750,12 +6551,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6783,37 +6584,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129386187</v>
+        <v>124175453</v>
       </c>
       <c r="B58" t="n">
-        <v>91561</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6821,13 +6631,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461816</v>
+        <v>461792</v>
       </c>
       <c r="R58" t="n">
-        <v>6700916</v>
+        <v>6700952</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6851,12 +6661,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,42 +6694,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129386062</v>
+        <v>124175534</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6927,13 +6741,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461861</v>
+        <v>461735</v>
       </c>
       <c r="R59" t="n">
-        <v>6700879</v>
+        <v>6701055</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6957,17 +6771,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6976,6 +6785,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6994,37 +6804,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385764</v>
+        <v>124176275</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7032,13 +6851,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461972</v>
+        <v>461688</v>
       </c>
       <c r="R60" t="n">
-        <v>6700967</v>
+        <v>6700885</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7062,12 +6881,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7095,37 +6914,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385673</v>
+        <v>124176290</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7133,13 +6961,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461869</v>
+        <v>461688</v>
       </c>
       <c r="R61" t="n">
-        <v>6700980</v>
+        <v>6700877</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7163,12 +6991,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7196,37 +7024,46 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129385729</v>
+        <v>124176306</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7234,13 +7071,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461948</v>
+        <v>461677</v>
       </c>
       <c r="R62" t="n">
-        <v>6700980</v>
+        <v>6700883</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7264,12 +7101,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7297,42 +7134,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129385644</v>
+        <v>129385966</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7340,10 +7181,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461812</v>
+        <v>461831</v>
       </c>
       <c r="R63" t="n">
-        <v>6700990</v>
+        <v>6700895</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7378,17 +7219,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7407,42 +7244,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129385937</v>
+        <v>129386288</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7450,10 +7291,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461930</v>
+        <v>461678</v>
       </c>
       <c r="R64" t="n">
-        <v>6700825</v>
+        <v>6700995</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7488,17 +7329,13 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7520,7 +7357,7 @@
         <v>129386570</v>
       </c>
       <c r="B65" t="n">
-        <v>98778</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7624,115 +7461,6 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>129386729</v>
-      </c>
-      <c r="B66" t="n">
-        <v>92915</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>L. Rutsberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>461658</v>
-      </c>
-      <c r="R66" t="n">
-        <v>6700848</v>
-      </c>
-      <c r="S66" t="n">
-        <v>25</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vansbro</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Järna</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386272</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386326</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174932</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386382</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386181</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386187</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176373</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386729</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174911</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175739</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176021</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385654</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385669</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174681</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2837,6 +2942,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174819</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175587</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3057,6 +3172,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385644</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3167,6 +3287,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386049</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3402,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386062</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3387,6 +3517,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386082</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386134</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3607,6 +3747,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386225</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3717,6 +3862,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386256</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3827,6 +3977,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386365</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3937,6 +4092,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386552</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4047,6 +4207,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386584</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4157,6 +4322,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386716</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4266,6 +4436,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175647</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4376,6 +4551,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175050</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4486,6 +4666,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175075</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4596,6 +4781,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175453</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4706,6 +4896,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175534</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4816,6 +5011,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176275</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176290</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5036,6 +5241,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124176306</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5146,6 +5356,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385966</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5256,6 +5471,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386288</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5366,6 +5586,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386570</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5467,6 +5692,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385684</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5568,6 +5798,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385719</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5669,6 +5904,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175215</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5770,6 +6010,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175266</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5871,6 +6116,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175346</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5972,6 +6222,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385673</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6073,6 +6328,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385729</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6174,6 +6434,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385753</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6275,6 +6540,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385764</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6376,6 +6646,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385780</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6477,6 +6752,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385788</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6578,6 +6858,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385794</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6691,6 +6976,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124174707</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6801,6 +7091,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175498</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6911,6 +7206,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385867</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7021,6 +7321,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129385937</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7131,6 +7436,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129386074</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7241,6 +7551,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175111</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7351,6 +7666,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175156</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7461,8 +7781,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175319</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ65"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4330,44 +4330,40 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124175647</v>
+        <v>135802943</v>
       </c>
       <c r="B35" t="n">
-        <v>57141</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4377,10 +4373,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461689</v>
+        <v>461661</v>
       </c>
       <c r="R35" t="n">
-        <v>6701105</v>
+        <v>6700753</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4407,12 +4403,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,52 +4439,52 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175647</t>
+          <t>https://artportalen.se/Sighting/135802943</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124175050</v>
+        <v>124175647</v>
       </c>
       <c r="B36" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4491,10 +4492,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461862</v>
+        <v>461689</v>
       </c>
       <c r="R36" t="n">
-        <v>6700845</v>
+        <v>6701105</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4535,7 +4536,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4553,13 +4553,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175050</t>
+          <t>https://artportalen.se/Sighting/124175647</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124175075</v>
+        <v>124175050</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461846</v>
+        <v>461862</v>
       </c>
       <c r="R37" t="n">
-        <v>6700848</v>
+        <v>6700845</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4668,13 +4668,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175075</t>
+          <t>https://artportalen.se/Sighting/124175050</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124175453</v>
+        <v>124175075</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461792</v>
+        <v>461846</v>
       </c>
       <c r="R38" t="n">
-        <v>6700952</v>
+        <v>6700848</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4783,13 +4783,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175453</t>
+          <t>https://artportalen.se/Sighting/124175075</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124175534</v>
+        <v>124175453</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461735</v>
+        <v>461792</v>
       </c>
       <c r="R39" t="n">
-        <v>6701055</v>
+        <v>6700952</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4898,13 +4898,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175534</t>
+          <t>https://artportalen.se/Sighting/124175453</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124176275</v>
+        <v>124175534</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461688</v>
+        <v>461735</v>
       </c>
       <c r="R40" t="n">
-        <v>6700885</v>
+        <v>6701055</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5013,13 +5013,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124176275</t>
+          <t>https://artportalen.se/Sighting/124175534</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124176290</v>
+        <v>124176275</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5069,7 +5069,7 @@
         <v>461688</v>
       </c>
       <c r="R41" t="n">
-        <v>6700877</v>
+        <v>6700885</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5128,13 +5128,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124176290</t>
+          <t>https://artportalen.se/Sighting/124176275</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124176306</v>
+        <v>124176290</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461677</v>
+        <v>461688</v>
       </c>
       <c r="R42" t="n">
-        <v>6700883</v>
+        <v>6700877</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5243,13 +5243,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124176306</t>
+          <t>https://artportalen.se/Sighting/124176290</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129385966</v>
+        <v>124176306</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5296,13 +5296,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461831</v>
+        <v>461677</v>
       </c>
       <c r="R43" t="n">
-        <v>6700895</v>
+        <v>6700883</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,13 +5358,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385966</t>
+          <t>https://artportalen.se/Sighting/124176306</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129386288</v>
+        <v>129385966</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461678</v>
+        <v>461831</v>
       </c>
       <c r="R44" t="n">
-        <v>6700995</v>
+        <v>6700895</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5473,13 +5473,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386288</t>
+          <t>https://artportalen.se/Sighting/129385966</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129386570</v>
+        <v>129386288</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461630</v>
+        <v>461678</v>
       </c>
       <c r="R45" t="n">
-        <v>6700920</v>
+        <v>6700995</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,43 +5588,52 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386570</t>
+          <t>https://artportalen.se/Sighting/129386288</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129385684</v>
+        <v>129386570</v>
       </c>
       <c r="B46" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5632,10 +5641,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461868</v>
+        <v>461630</v>
       </c>
       <c r="R46" t="n">
-        <v>6700949</v>
+        <v>6700920</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5694,38 +5703,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385684</t>
+          <t>https://artportalen.se/Sighting/129386570</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129385719</v>
+        <v>129385684</v>
       </c>
       <c r="B47" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5738,10 +5747,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461960</v>
+        <v>461868</v>
       </c>
       <c r="R47" t="n">
-        <v>6700956</v>
+        <v>6700949</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5800,38 +5809,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385719</t>
+          <t>https://artportalen.se/Sighting/129385684</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124175215</v>
+        <v>129385719</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5844,13 +5853,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461931</v>
+        <v>461960</v>
       </c>
       <c r="R48" t="n">
-        <v>6700883</v>
+        <v>6700956</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5874,12 +5883,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5906,13 +5915,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175215</t>
+          <t>https://artportalen.se/Sighting/129385719</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124175266</v>
+        <v>124175215</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5950,10 +5959,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461917</v>
+        <v>461931</v>
       </c>
       <c r="R49" t="n">
-        <v>6700885</v>
+        <v>6700883</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6012,13 +6021,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175266</t>
+          <t>https://artportalen.se/Sighting/124175215</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124175346</v>
+        <v>124175266</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -6056,10 +6065,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461868</v>
+        <v>461917</v>
       </c>
       <c r="R50" t="n">
-        <v>6700927</v>
+        <v>6700885</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6118,13 +6127,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175346</t>
+          <t>https://artportalen.se/Sighting/124175266</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129385673</v>
+        <v>124175346</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6162,13 +6171,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461869</v>
+        <v>461868</v>
       </c>
       <c r="R51" t="n">
-        <v>6700980</v>
+        <v>6700927</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6192,12 +6201,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6224,13 +6233,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385673</t>
+          <t>https://artportalen.se/Sighting/124175346</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129385729</v>
+        <v>129385673</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6268,7 +6277,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461948</v>
+        <v>461869</v>
       </c>
       <c r="R52" t="n">
         <v>6700980</v>
@@ -6330,13 +6339,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385729</t>
+          <t>https://artportalen.se/Sighting/129385673</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129385753</v>
+        <v>129385729</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6374,10 +6383,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461960</v>
+        <v>461948</v>
       </c>
       <c r="R53" t="n">
-        <v>6700969</v>
+        <v>6700980</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6436,13 +6445,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385753</t>
+          <t>https://artportalen.se/Sighting/129385729</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129385764</v>
+        <v>129385753</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6480,10 +6489,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461972</v>
+        <v>461960</v>
       </c>
       <c r="R54" t="n">
-        <v>6700967</v>
+        <v>6700969</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6542,13 +6551,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385764</t>
+          <t>https://artportalen.se/Sighting/129385753</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129385780</v>
+        <v>129385764</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6586,10 +6595,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461935</v>
+        <v>461972</v>
       </c>
       <c r="R55" t="n">
-        <v>6700926</v>
+        <v>6700967</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6648,13 +6657,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385780</t>
+          <t>https://artportalen.se/Sighting/129385764</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129385788</v>
+        <v>129385780</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6692,10 +6701,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461925</v>
+        <v>461935</v>
       </c>
       <c r="R56" t="n">
-        <v>6700914</v>
+        <v>6700926</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6754,13 +6763,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385788</t>
+          <t>https://artportalen.se/Sighting/129385780</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129385794</v>
+        <v>129385788</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6798,10 +6807,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461932</v>
+        <v>461925</v>
       </c>
       <c r="R57" t="n">
-        <v>6700907</v>
+        <v>6700914</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6860,56 +6869,43 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385794</t>
+          <t>https://artportalen.se/Sighting/129385788</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124174707</v>
+        <v>129385794</v>
       </c>
       <c r="B58" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6917,13 +6913,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461884</v>
+        <v>461932</v>
       </c>
       <c r="R58" t="n">
-        <v>6700921</v>
+        <v>6700907</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6947,12 +6943,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6961,6 +6957,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6978,13 +6975,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124174707</t>
+          <t>https://artportalen.se/Sighting/129385794</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124175498</v>
+        <v>124174707</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7012,12 +7009,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7027,10 +7032,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461876</v>
+        <v>461884</v>
       </c>
       <c r="R59" t="n">
-        <v>6700933</v>
+        <v>6700921</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7065,11 +7070,6 @@
           <t>2025-04-17</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7093,13 +7093,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175498</t>
+          <t>https://artportalen.se/Sighting/124174707</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129385867</v>
+        <v>124175498</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461920</v>
+        <v>461876</v>
       </c>
       <c r="R60" t="n">
-        <v>6700812</v>
+        <v>6700933</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7172,17 +7172,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7208,13 +7208,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385867</t>
+          <t>https://artportalen.se/Sighting/124175498</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129385937</v>
+        <v>129385867</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461930</v>
+        <v>461920</v>
       </c>
       <c r="R61" t="n">
-        <v>6700825</v>
+        <v>6700812</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7323,13 +7323,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385937</t>
+          <t>https://artportalen.se/Sighting/129385867</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129386074</v>
+        <v>129385937</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -7362,7 +7362,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461874</v>
+        <v>461930</v>
       </c>
       <c r="R62" t="n">
-        <v>6700850</v>
+        <v>6700825</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7438,52 +7438,48 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386074</t>
+          <t>https://artportalen.se/Sighting/129385937</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124175111</v>
+        <v>129386074</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7491,13 +7487,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461897</v>
+        <v>461874</v>
       </c>
       <c r="R63" t="n">
-        <v>6700803</v>
+        <v>6700850</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7521,12 +7517,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7535,7 +7536,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7553,13 +7553,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175111</t>
+          <t>https://artportalen.se/Sighting/129386074</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124175156</v>
+        <v>124175111</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461943</v>
+        <v>461897</v>
       </c>
       <c r="R64" t="n">
-        <v>6700846</v>
+        <v>6700803</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7668,13 +7668,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124175156</t>
+          <t>https://artportalen.se/Sighting/124175111</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124175319</v>
+        <v>124175156</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461910</v>
+        <v>461943</v>
       </c>
       <c r="R65" t="n">
-        <v>6700899</v>
+        <v>6700846</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7782,6 +7782,121 @@
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124175156</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124175319</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L. Rutsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>461910</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6700899</v>
+      </c>
+      <c r="S66" t="n">
+        <v>50</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124175319</t>
         </is>
@@ -7853,6 +7968,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4333,7 +4333,7 @@
         <v>135802943</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4333,7 +4333,7 @@
         <v>135802943</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4333,7 +4333,7 @@
         <v>135802943</v>
       </c>
       <c r="B35" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11713-2025 artfynd.xlsx
+++ b/artfynd/A 11713-2025 artfynd.xlsx
@@ -4333,7 +4333,7 @@
         <v>135802943</v>
       </c>
       <c r="B35" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
